--- a/СМіП/лабиСтатистичне_моделювання.xlsx
+++ b/СМіП/лабиСтатистичне_моделювання.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trock\Desktop\SMT\СМіП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EBB84D-6654-49A1-9AC2-AA97A2F719B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECAD84D-0DB2-4F28-ADF1-C0115E354119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="4" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="5" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ЛР1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,11 @@
     <sheet name="ЛР3" sheetId="3" r:id="rId3"/>
     <sheet name="ЛР4" sheetId="4" r:id="rId4"/>
     <sheet name="ЛР5" sheetId="5" r:id="rId5"/>
+    <sheet name="ЛР6" sheetId="6" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -60,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="115">
   <si>
     <t>№</t>
   </si>
@@ -424,6 +428,69 @@
   <si>
     <t>RYX1X2</t>
   </si>
+  <si>
+    <t>t^2</t>
+  </si>
+  <si>
+    <t>Місяць</t>
+  </si>
+  <si>
+    <t>Обсяг (yi​), млн грн</t>
+  </si>
+  <si>
+    <t>Абсолютний приріст</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коеф. зростання </t>
+  </si>
+  <si>
+    <t>Темпи зростання</t>
+  </si>
+  <si>
+    <t>Коефіціент приросту</t>
+  </si>
+  <si>
+    <t>Темпи прирост</t>
+  </si>
+  <si>
+    <t>Абсолютні значення на 1%</t>
+  </si>
+  <si>
+    <t>Зглажування ряду</t>
+  </si>
+  <si>
+    <t>З попер.</t>
+  </si>
+  <si>
+    <t>З місяцем 1</t>
+  </si>
+  <si>
+    <t>Kp</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Середній абсолют</t>
+  </si>
+  <si>
+    <t>Тр</t>
+  </si>
+  <si>
+    <t>Тпр</t>
+  </si>
+  <si>
+    <t>Аналітичне зглажування ряду динаміки рівнянням прямої</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>yt</t>
+  </si>
+  <si>
+    <t>Кількість n</t>
+  </si>
 </sst>
 </file>
 
@@ -432,7 +499,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -523,6 +590,30 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -545,7 +636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -568,12 +659,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -599,6 +684,48 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1593,6 +1720,437 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Поточний</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ЛР6!$A$3:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ЛР6!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>141.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>143.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>146.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>149</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9A58-49D2-B751-B3FE107D168D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Аналтичний</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ЛР6!$A$18:$A$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ЛР6!$E$18:$E$24</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>140.67500000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>142.02142857142857</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>143.36785714285716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>144.71428571428572</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>146.06071428571428</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>147.40714285714287</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>148.75357142857143</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9A58-49D2-B751-B3FE107D168D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1101487088"/>
+        <c:axId val="1101488048"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1101487088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1101488048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1101488048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1101487088"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1634,6 +2192,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2705,6 +3303,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2785,6 +3899,155 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>259556</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>616744</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF01FBB7-65B1-D02D-A53F-E1EC971E3745}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Аркуш1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="A3">
+            <v>1</v>
+          </cell>
+          <cell r="B3">
+            <v>141.30000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>2</v>
+          </cell>
+          <cell r="B4">
+            <v>140.5</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>3</v>
+          </cell>
+          <cell r="B5">
+            <v>143.4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>4</v>
+          </cell>
+          <cell r="B6">
+            <v>146.80000000000001</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>5</v>
+          </cell>
+          <cell r="B7">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>6</v>
+          </cell>
+          <cell r="B8">
+            <v>147</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>7</v>
+          </cell>
+          <cell r="B9">
+            <v>149</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>140.67500000000001</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>142.02142857142857</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20">
+            <v>143.36785714285716</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21">
+            <v>144.71428571428572</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22">
+            <v>146.06071428571428</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23">
+            <v>147.40714285714287</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24">
+            <v>148.75357142857143</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4436,20 +5699,20 @@
       <c r="M13" s="7"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
@@ -4635,10 +5898,10 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="11"/>
+      <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
@@ -4650,10 +5913,10 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="12"/>
+      <c r="B26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
@@ -5275,2043 +6538,3539 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:39" ht="81" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A2" s="13">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>12</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>17.600000000000001</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="12">
         <v>36.299999999999997</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="16">
         <f>D2*B2</f>
         <v>435.59999999999997</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="17">
         <f>D2*C2</f>
         <v>638.88</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="17">
         <f>B2*B2</f>
         <v>144</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="17">
         <f>C2*C2</f>
         <v>309.76000000000005</v>
       </c>
-      <c r="I2" s="19">
+      <c r="I2" s="17">
         <f>D2*D2</f>
         <v>1317.6899999999998</v>
       </c>
-      <c r="J2" s="19">
+      <c r="J2" s="17">
         <f>B2*C2</f>
         <v>211.20000000000002</v>
       </c>
-      <c r="K2" s="18">
+      <c r="K2" s="16">
         <f>$E$19+B2*$E$20+C2*$E$21</f>
         <v>34.176067904574907</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L2" s="15">
         <f>D2-K2</f>
         <v>2.12393209542509</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="17"/>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="17"/>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="17"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A3" s="13">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="11">
         <v>13.5</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="12">
         <v>20.8</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="12">
         <v>31.9</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="16">
         <f t="shared" ref="E3:E9" si="0">D3*B3</f>
         <v>430.65</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="17">
         <f t="shared" ref="F3:F9" si="1">D3*C3</f>
         <v>663.52</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="17">
         <f t="shared" ref="G3:I9" si="2">B3*B3</f>
         <v>182.25</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="17">
         <f t="shared" si="2"/>
         <v>432.64000000000004</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="17">
         <f t="shared" si="2"/>
         <v>1017.6099999999999</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="17">
         <f t="shared" ref="J3:J9" si="3">B3*C3</f>
         <v>280.8</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="16">
         <f t="shared" ref="K3:K9" si="4">$E$19+B3*$E$20+C3*$E$21</f>
         <v>33.585469199229216</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="15">
         <f t="shared" ref="L3:L9" si="5">D3-K3</f>
         <v>-1.6854691992292175</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-      <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17"/>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="17"/>
-      <c r="AB3" s="17"/>
-      <c r="AC3" s="17"/>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="17"/>
-      <c r="AF3" s="17"/>
-      <c r="AG3" s="17"/>
-      <c r="AH3" s="17"/>
-      <c r="AI3" s="17"/>
-      <c r="AJ3" s="17"/>
-      <c r="AK3" s="17"/>
-      <c r="AL3" s="17"/>
-      <c r="AM3" s="17"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="15"/>
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="15"/>
+      <c r="AH3" s="15"/>
+      <c r="AI3" s="15"/>
+      <c r="AJ3" s="15"/>
+      <c r="AK3" s="15"/>
+      <c r="AL3" s="15"/>
+      <c r="AM3" s="15"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="11">
         <v>14.2</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>14.4</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="12">
         <v>30.4</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="16">
         <f t="shared" si="0"/>
         <v>431.67999999999995</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="17">
         <f t="shared" si="1"/>
         <v>437.76</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="17">
         <f t="shared" si="2"/>
         <v>201.64</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="17">
         <f t="shared" si="2"/>
         <v>207.36</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="17">
         <f t="shared" si="2"/>
         <v>924.16</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="17">
         <f t="shared" si="3"/>
         <v>204.48</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="16">
         <f t="shared" si="4"/>
         <v>29.133759613732352</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="15">
         <f t="shared" si="5"/>
         <v>1.266240386267647</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="17"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="17"/>
-      <c r="AC4" s="17"/>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="17"/>
-      <c r="AF4" s="17"/>
-      <c r="AG4" s="17"/>
-      <c r="AH4" s="17"/>
-      <c r="AI4" s="17"/>
-      <c r="AJ4" s="17"/>
-      <c r="AK4" s="17"/>
-      <c r="AL4" s="17"/>
-      <c r="AM4" s="17"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15"/>
+      <c r="AL4" s="15"/>
+      <c r="AM4" s="15"/>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A5" s="13">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>11.6</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>18.100000000000001</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <v>36.1</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="16">
         <f t="shared" si="0"/>
         <v>418.76</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="17">
         <f t="shared" si="1"/>
         <v>653.41000000000008</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="17">
         <f t="shared" si="2"/>
         <v>134.56</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="17">
         <f t="shared" si="2"/>
         <v>327.61000000000007</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="17">
         <f t="shared" si="2"/>
         <v>1303.21</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="17">
         <f t="shared" si="3"/>
         <v>209.96</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="16">
         <f t="shared" si="4"/>
         <v>35.049563985434077</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="15">
         <f t="shared" si="5"/>
         <v>1.0504360145659248</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="17"/>
-      <c r="AH5" s="17"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="17"/>
-      <c r="AK5" s="17"/>
-      <c r="AL5" s="17"/>
-      <c r="AM5" s="17"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="15"/>
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="15"/>
+      <c r="AH5" s="15"/>
+      <c r="AI5" s="15"/>
+      <c r="AJ5" s="15"/>
+      <c r="AK5" s="15"/>
+      <c r="AL5" s="15"/>
+      <c r="AM5" s="15"/>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A6" s="13">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>12.7</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>19.899999999999999</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>32.799999999999997</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="16">
         <f t="shared" si="0"/>
         <v>416.55999999999995</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="17">
         <f t="shared" si="1"/>
         <v>652.71999999999991</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <f t="shared" si="2"/>
         <v>161.29</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="17">
         <f t="shared" si="2"/>
         <v>396.00999999999993</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="17">
         <f t="shared" si="2"/>
         <v>1075.8399999999999</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="17">
         <f t="shared" si="3"/>
         <v>252.72999999999996</v>
       </c>
-      <c r="K6" s="18">
+      <c r="K6" s="16">
         <f t="shared" si="4"/>
         <v>34.327235344008685</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="15">
         <f t="shared" si="5"/>
         <v>-1.5272353440086874</v>
       </c>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="17"/>
-      <c r="AH6" s="17"/>
-      <c r="AI6" s="17"/>
-      <c r="AJ6" s="17"/>
-      <c r="AK6" s="17"/>
-      <c r="AL6" s="17"/>
-      <c r="AM6" s="17"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="15"/>
+      <c r="AK6" s="15"/>
+      <c r="AL6" s="15"/>
+      <c r="AM6" s="15"/>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A7" s="13">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>14.4</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <v>17</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>29.5</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="16">
         <f t="shared" si="0"/>
         <v>424.8</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="17">
         <f t="shared" si="1"/>
         <v>501.5</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="17">
         <f t="shared" si="2"/>
         <v>207.36</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="17">
         <f t="shared" si="2"/>
         <v>289</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="17">
         <f t="shared" si="2"/>
         <v>870.25</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="17">
         <f t="shared" si="3"/>
         <v>244.8</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="16">
         <f t="shared" si="4"/>
         <v>30.204850598711079</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="15">
         <f t="shared" si="5"/>
         <v>-0.70485059871107936</v>
       </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="17"/>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="17"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="17"/>
-      <c r="AF7" s="17"/>
-      <c r="AG7" s="17"/>
-      <c r="AH7" s="17"/>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="17"/>
-      <c r="AK7" s="17"/>
-      <c r="AL7" s="17"/>
-      <c r="AM7" s="17"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="15"/>
+      <c r="AC7" s="15"/>
+      <c r="AD7" s="15"/>
+      <c r="AE7" s="15"/>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="15"/>
+      <c r="AH7" s="15"/>
+      <c r="AI7" s="15"/>
+      <c r="AJ7" s="15"/>
+      <c r="AK7" s="15"/>
+      <c r="AL7" s="15"/>
+      <c r="AM7" s="15"/>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A8" s="13">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>18.399999999999999</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <v>11.7</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>23.2</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="16">
         <f t="shared" si="0"/>
         <v>426.87999999999994</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="17">
         <f t="shared" si="1"/>
         <v>271.44</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="17">
         <f t="shared" si="2"/>
         <v>338.55999999999995</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="17">
         <f t="shared" si="2"/>
         <v>136.88999999999999</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="17">
         <f t="shared" si="2"/>
         <v>538.24</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="17">
         <f t="shared" si="3"/>
         <v>215.27999999999997</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K8" s="16">
         <f t="shared" si="4"/>
         <v>21.311169892707952</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="15">
         <f t="shared" si="5"/>
         <v>1.8888301072920477</v>
       </c>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="17"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="17"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="17"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="15"/>
+      <c r="AC8" s="15"/>
+      <c r="AD8" s="15"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="15"/>
+      <c r="AH8" s="15"/>
+      <c r="AI8" s="15"/>
+      <c r="AJ8" s="15"/>
+      <c r="AK8" s="15"/>
+      <c r="AL8" s="15"/>
+      <c r="AM8" s="15"/>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A9" s="13">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="11">
         <v>15.8</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <v>8</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <v>20.9</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="16">
         <f t="shared" si="0"/>
         <v>330.21999999999997</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="17">
         <f t="shared" si="1"/>
         <v>167.2</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="17">
         <f t="shared" si="2"/>
         <v>249.64000000000001</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="17">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="17">
         <f t="shared" si="2"/>
         <v>436.80999999999995</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="17">
         <f t="shared" si="3"/>
         <v>126.4</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="16">
         <f t="shared" si="4"/>
         <v>23.311883461595098</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="15">
         <f t="shared" si="5"/>
         <v>-2.4118834615950995</v>
       </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="17"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="17"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="17"/>
-      <c r="AM9" s="17"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="15"/>
+      <c r="AC9" s="15"/>
+      <c r="AD9" s="15"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="15"/>
+      <c r="AH9" s="15"/>
+      <c r="AI9" s="15"/>
+      <c r="AJ9" s="15"/>
+      <c r="AK9" s="15"/>
+      <c r="AL9" s="15"/>
+      <c r="AM9" s="15"/>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
-      <c r="AK10" s="17"/>
-      <c r="AL10" s="17"/>
-      <c r="AM10" s="17"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="15"/>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-      <c r="AM11" s="17"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15"/>
+      <c r="AB11" s="15"/>
+      <c r="AC11" s="15"/>
+      <c r="AD11" s="15"/>
+      <c r="AE11" s="15"/>
+      <c r="AF11" s="15"/>
+      <c r="AG11" s="15"/>
+      <c r="AH11" s="15"/>
+      <c r="AI11" s="15"/>
+      <c r="AJ11" s="15"/>
+      <c r="AK11" s="15"/>
+      <c r="AL11" s="15"/>
+      <c r="AM11" s="15"/>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="15">
         <f>SUM(B2:B9)</f>
         <v>112.60000000000001</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="15">
         <f t="shared" ref="C12:L12" si="6">SUM(C2:C9)</f>
         <v>127.50000000000001</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="15">
         <f t="shared" si="6"/>
         <v>241.1</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="15">
         <f t="shared" si="6"/>
         <v>3315.15</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <f t="shared" si="6"/>
         <v>3986.43</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="15">
         <f t="shared" si="6"/>
         <v>1619.3</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="15">
         <f t="shared" si="6"/>
         <v>2163.27</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="15">
         <f t="shared" si="6"/>
         <v>7483.8099999999995</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="15">
         <f t="shared" si="6"/>
         <v>1745.65</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="15">
         <f t="shared" si="6"/>
         <v>241.0999999999934</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="15">
         <f t="shared" si="6"/>
         <v>6.6258110109629342E-12</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-      <c r="AH12" s="17"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="17"/>
-      <c r="AM12" s="17"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="15"/>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="15"/>
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="15"/>
+      <c r="AJ12" s="15"/>
+      <c r="AK12" s="15"/>
+      <c r="AL12" s="15"/>
+      <c r="AM12" s="15"/>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="15">
         <f>B12/$A$9</f>
         <v>14.075000000000001</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="15">
         <f t="shared" ref="C13:L13" si="7">C12/$A$9</f>
         <v>15.937500000000002</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="15">
         <f t="shared" si="7"/>
         <v>30.137499999999999</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="15">
         <f t="shared" si="7"/>
         <v>414.39375000000001</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="15">
         <f t="shared" si="7"/>
         <v>498.30374999999998</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="15">
         <f t="shared" si="7"/>
         <v>202.41249999999999</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <f t="shared" si="7"/>
         <v>270.40875</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="15">
         <f t="shared" si="7"/>
         <v>935.47624999999994</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="15">
         <f t="shared" si="7"/>
         <v>218.20625000000001</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="15">
         <f t="shared" si="7"/>
         <v>30.137499999999175</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="15">
         <f t="shared" si="7"/>
         <v>8.2822637637036678E-13</v>
       </c>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
-      <c r="AG13" s="17"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="17"/>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="15"/>
+      <c r="AC13" s="15"/>
+      <c r="AD13" s="15"/>
+      <c r="AE13" s="15"/>
+      <c r="AF13" s="15"/>
+      <c r="AG13" s="15"/>
+      <c r="AH13" s="15"/>
+      <c r="AI13" s="15"/>
+      <c r="AJ13" s="15"/>
+      <c r="AK13" s="15"/>
+      <c r="AL13" s="15"/>
+      <c r="AM13" s="15"/>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="17"/>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="17"/>
-      <c r="AF14" s="17"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="17"/>
-      <c r="AI14" s="17"/>
-      <c r="AJ14" s="17"/>
-      <c r="AK14" s="17"/>
-      <c r="AL14" s="17"/>
-      <c r="AM14" s="17"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
+      <c r="AD14" s="15"/>
+      <c r="AE14" s="15"/>
+      <c r="AF14" s="15"/>
+      <c r="AG14" s="15"/>
+      <c r="AH14" s="15"/>
+      <c r="AI14" s="15"/>
+      <c r="AJ14" s="15"/>
+      <c r="AK14" s="15"/>
+      <c r="AL14" s="15"/>
+      <c r="AM14" s="15"/>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A15" s="17">
+      <c r="A15" s="15">
         <f>$D$12</f>
         <v>241.1</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="15">
         <f>$A$9</f>
         <v>8</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="15">
         <f>$B$12</f>
         <v>112.60000000000001</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="15">
         <f>$C$12</f>
         <v>127.50000000000001</v>
       </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17">
+      <c r="E15" s="15"/>
+      <c r="F15" s="15">
         <f>$D$12</f>
         <v>241.1</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="15">
         <f>$B$12</f>
         <v>112.60000000000001</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="15">
         <f>$C$12</f>
         <v>127.50000000000001</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17">
+      <c r="I15" s="15"/>
+      <c r="J15" s="15">
         <f>$A$9</f>
         <v>8</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="15">
         <f>$D$12</f>
         <v>241.1</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="15">
         <f>$C$12</f>
         <v>127.50000000000001</v>
       </c>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17">
+      <c r="M15" s="15"/>
+      <c r="N15" s="15">
         <f>$A$9</f>
         <v>8</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="15">
         <f>$B$12</f>
         <v>112.60000000000001</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="15">
         <f>$D$12</f>
         <v>241.1</v>
       </c>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="17"/>
-      <c r="AE15" s="17"/>
-      <c r="AF15" s="17"/>
-      <c r="AG15" s="17"/>
-      <c r="AH15" s="17"/>
-      <c r="AI15" s="17"/>
-      <c r="AJ15" s="17"/>
-      <c r="AK15" s="17"/>
-      <c r="AL15" s="17"/>
-      <c r="AM15" s="17"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
+      <c r="AC15" s="15"/>
+      <c r="AD15" s="15"/>
+      <c r="AE15" s="15"/>
+      <c r="AF15" s="15"/>
+      <c r="AG15" s="15"/>
+      <c r="AH15" s="15"/>
+      <c r="AI15" s="15"/>
+      <c r="AJ15" s="15"/>
+      <c r="AK15" s="15"/>
+      <c r="AL15" s="15"/>
+      <c r="AM15" s="15"/>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A16" s="17">
+      <c r="A16" s="15">
         <f>$E$12</f>
         <v>3315.15</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="18">
         <f>$B$12</f>
         <v>112.60000000000001</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="15">
         <f>$G$12</f>
         <v>1619.3</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="15">
         <f>$J$12</f>
         <v>1745.65</v>
       </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17">
+      <c r="E16" s="15"/>
+      <c r="F16" s="15">
         <f>$E$12</f>
         <v>3315.15</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="15">
         <f>$G$12</f>
         <v>1619.3</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="15">
         <f>$J$12</f>
         <v>1745.65</v>
       </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="20">
+      <c r="I16" s="15"/>
+      <c r="J16" s="18">
         <f>$B$12</f>
         <v>112.60000000000001</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="15">
         <f>$E$12</f>
         <v>3315.15</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="15">
         <f>$J$12</f>
         <v>1745.65</v>
       </c>
-      <c r="M16" s="17"/>
-      <c r="N16" s="20">
+      <c r="M16" s="15"/>
+      <c r="N16" s="18">
         <f>$B$12</f>
         <v>112.60000000000001</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="15">
         <f>$G$12</f>
         <v>1619.3</v>
       </c>
-      <c r="P16" s="17">
+      <c r="P16" s="15">
         <f>$E$12</f>
         <v>3315.15</v>
       </c>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17"/>
-      <c r="AA16" s="17"/>
-      <c r="AB16" s="17"/>
-      <c r="AC16" s="17"/>
-      <c r="AD16" s="17"/>
-      <c r="AE16" s="17"/>
-      <c r="AF16" s="17"/>
-      <c r="AG16" s="17"/>
-      <c r="AH16" s="17"/>
-      <c r="AI16" s="17"/>
-      <c r="AJ16" s="17"/>
-      <c r="AK16" s="17"/>
-      <c r="AL16" s="17"/>
-      <c r="AM16" s="17"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="15"/>
+      <c r="AA16" s="15"/>
+      <c r="AB16" s="15"/>
+      <c r="AC16" s="15"/>
+      <c r="AD16" s="15"/>
+      <c r="AE16" s="15"/>
+      <c r="AF16" s="15"/>
+      <c r="AG16" s="15"/>
+      <c r="AH16" s="15"/>
+      <c r="AI16" s="15"/>
+      <c r="AJ16" s="15"/>
+      <c r="AK16" s="15"/>
+      <c r="AL16" s="15"/>
+      <c r="AM16" s="15"/>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A17" s="17">
+      <c r="A17" s="15">
         <f>$F$12</f>
         <v>3986.43</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="15">
         <f>$C$12</f>
         <v>127.50000000000001</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="15">
         <f>$J$12</f>
         <v>1745.65</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="15">
         <f>$H$12</f>
         <v>2163.27</v>
       </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17">
+      <c r="E17" s="15"/>
+      <c r="F17" s="15">
         <f>$F$12</f>
         <v>3986.43</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="15">
         <f>$J$12</f>
         <v>1745.65</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <f>$H$12</f>
         <v>2163.27</v>
       </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17">
+      <c r="I17" s="15"/>
+      <c r="J17" s="15">
         <f>$C$12</f>
         <v>127.50000000000001</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="15">
         <f>$F$12</f>
         <v>3986.43</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="15">
         <f>$H$12</f>
         <v>2163.27</v>
       </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17">
+      <c r="M17" s="15"/>
+      <c r="N17" s="15">
         <f>$C$12</f>
         <v>127.50000000000001</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="15">
         <f>$J$12</f>
         <v>1745.65</v>
       </c>
-      <c r="P17" s="17">
+      <c r="P17" s="15">
         <f>$F$12</f>
         <v>3986.43</v>
       </c>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="17"/>
-      <c r="AA17" s="17"/>
-      <c r="AB17" s="17"/>
-      <c r="AC17" s="17"/>
-      <c r="AD17" s="17"/>
-      <c r="AE17" s="17"/>
-      <c r="AF17" s="17"/>
-      <c r="AG17" s="17"/>
-      <c r="AH17" s="17"/>
-      <c r="AI17" s="17"/>
-      <c r="AJ17" s="17"/>
-      <c r="AK17" s="17"/>
-      <c r="AL17" s="17"/>
-      <c r="AM17" s="17"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="15"/>
+      <c r="AK17" s="15"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="15"/>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="17"/>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="17"/>
-      <c r="AD18" s="17"/>
-      <c r="AE18" s="17"/>
-      <c r="AF18" s="17"/>
-      <c r="AG18" s="17"/>
-      <c r="AH18" s="17"/>
-      <c r="AI18" s="17"/>
-      <c r="AJ18" s="17"/>
-      <c r="AK18" s="17"/>
-      <c r="AL18" s="17"/>
-      <c r="AM18" s="17"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="15"/>
+      <c r="AC18" s="15"/>
+      <c r="AD18" s="15"/>
+      <c r="AE18" s="15"/>
+      <c r="AF18" s="15"/>
+      <c r="AG18" s="15"/>
+      <c r="AH18" s="15"/>
+      <c r="AI18" s="15"/>
+      <c r="AJ18" s="15"/>
+      <c r="AK18" s="15"/>
+      <c r="AL18" s="15"/>
+      <c r="AM18" s="15"/>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="15">
         <f>MDETERM(B15:D17)</f>
         <v>17035.187799999876</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="22" t="s">
+      <c r="C19" s="15"/>
+      <c r="D19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="15">
         <f>B20/B19</f>
         <v>43.133388144977772</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="17"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="17"/>
-      <c r="AF19" s="17"/>
-      <c r="AG19" s="17"/>
-      <c r="AH19" s="17"/>
-      <c r="AI19" s="17"/>
-      <c r="AJ19" s="17"/>
-      <c r="AK19" s="17"/>
-      <c r="AL19" s="17"/>
-      <c r="AM19" s="17"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="15"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
+      <c r="Z19" s="15"/>
+      <c r="AA19" s="15"/>
+      <c r="AB19" s="15"/>
+      <c r="AC19" s="15"/>
+      <c r="AD19" s="15"/>
+      <c r="AE19" s="15"/>
+      <c r="AF19" s="15"/>
+      <c r="AG19" s="15"/>
+      <c r="AH19" s="15"/>
+      <c r="AI19" s="15"/>
+      <c r="AJ19" s="15"/>
+      <c r="AK19" s="15"/>
+      <c r="AL19" s="15"/>
+      <c r="AM19" s="15"/>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="15">
         <f>MDETERM(F15:H17)</f>
         <v>734785.36749998468</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="22" t="s">
+      <c r="C20" s="15"/>
+      <c r="D20" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="15">
         <f>B21/B19</f>
         <v>-1.5224072962670918</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-      <c r="T20" s="17"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
-      <c r="X20" s="17"/>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="17"/>
-      <c r="AA20" s="17"/>
-      <c r="AB20" s="17"/>
-      <c r="AC20" s="17"/>
-      <c r="AD20" s="17"/>
-      <c r="AE20" s="17"/>
-      <c r="AF20" s="17"/>
-      <c r="AG20" s="17"/>
-      <c r="AH20" s="17"/>
-      <c r="AI20" s="17"/>
-      <c r="AJ20" s="17"/>
-      <c r="AK20" s="17"/>
-      <c r="AL20" s="17"/>
-      <c r="AM20" s="17"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15"/>
+      <c r="AB20" s="15"/>
+      <c r="AC20" s="15"/>
+      <c r="AD20" s="15"/>
+      <c r="AE20" s="15"/>
+      <c r="AF20" s="15"/>
+      <c r="AG20" s="15"/>
+      <c r="AH20" s="15"/>
+      <c r="AI20" s="15"/>
+      <c r="AJ20" s="15"/>
+      <c r="AK20" s="15"/>
+      <c r="AL20" s="15"/>
+      <c r="AM20" s="15"/>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="15">
         <f>MDETERM(J15:L17)</f>
         <v>-25934.494199999961</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="22" t="s">
+      <c r="C21" s="15"/>
+      <c r="D21" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="15">
         <f>B22/B19</f>
         <v>0.5290663247046723</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="17"/>
-      <c r="AA21" s="17"/>
-      <c r="AB21" s="17"/>
-      <c r="AC21" s="17"/>
-      <c r="AD21" s="17"/>
-      <c r="AE21" s="17"/>
-      <c r="AF21" s="17"/>
-      <c r="AG21" s="17"/>
-      <c r="AH21" s="17"/>
-      <c r="AI21" s="17"/>
-      <c r="AJ21" s="17"/>
-      <c r="AK21" s="17"/>
-      <c r="AL21" s="17"/>
-      <c r="AM21" s="17"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15"/>
+      <c r="AB21" s="15"/>
+      <c r="AC21" s="15"/>
+      <c r="AD21" s="15"/>
+      <c r="AE21" s="15"/>
+      <c r="AF21" s="15"/>
+      <c r="AG21" s="15"/>
+      <c r="AH21" s="15"/>
+      <c r="AI21" s="15"/>
+      <c r="AJ21" s="15"/>
+      <c r="AK21" s="15"/>
+      <c r="AL21" s="15"/>
+      <c r="AM21" s="15"/>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="15">
         <f>MDETERM(N15:P17)</f>
         <v>9012.7441999998064</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
-      <c r="AA22" s="17"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="17"/>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="17"/>
-      <c r="AF22" s="17"/>
-      <c r="AG22" s="17"/>
-      <c r="AH22" s="17"/>
-      <c r="AI22" s="17"/>
-      <c r="AJ22" s="17"/>
-      <c r="AK22" s="17"/>
-      <c r="AL22" s="17"/>
-      <c r="AM22" s="17"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="15"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15"/>
+      <c r="AB22" s="15"/>
+      <c r="AC22" s="15"/>
+      <c r="AD22" s="15"/>
+      <c r="AE22" s="15"/>
+      <c r="AF22" s="15"/>
+      <c r="AG22" s="15"/>
+      <c r="AH22" s="15"/>
+      <c r="AI22" s="15"/>
+      <c r="AJ22" s="15"/>
+      <c r="AK22" s="15"/>
+      <c r="AL22" s="15"/>
+      <c r="AM22" s="15"/>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="17"/>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17"/>
-      <c r="AC23" s="17"/>
-      <c r="AD23" s="17"/>
-      <c r="AE23" s="17"/>
-      <c r="AF23" s="17"/>
-      <c r="AG23" s="17"/>
-      <c r="AH23" s="17"/>
-      <c r="AI23" s="17"/>
-      <c r="AJ23" s="17"/>
-      <c r="AK23" s="17"/>
-      <c r="AL23" s="17"/>
-      <c r="AM23" s="17"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
+      <c r="AB23" s="15"/>
+      <c r="AC23" s="15"/>
+      <c r="AD23" s="15"/>
+      <c r="AE23" s="15"/>
+      <c r="AF23" s="15"/>
+      <c r="AG23" s="15"/>
+      <c r="AH23" s="15"/>
+      <c r="AI23" s="15"/>
+      <c r="AJ23" s="15"/>
+      <c r="AK23" s="15"/>
+      <c r="AL23" s="15"/>
+      <c r="AM23" s="15"/>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="15">
         <f>SQRT(G13-POWER(B13,2))</f>
         <v>2.0753011829611534</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17" t="s">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="15">
         <f>ABS(E20)*(B24*SQRT(1-B29^2)*SQRT(7-3-1))/(B26*SQRT(1-B30^2))</f>
         <v>2.2506166362999229</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17" t="s">
+      <c r="F24" s="15"/>
+      <c r="G24" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="15">
         <f>E20*(B13)/(D13)</f>
         <v>-0.71100398821930555</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="17"/>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="17"/>
-      <c r="AF24" s="17"/>
-      <c r="AG24" s="17"/>
-      <c r="AH24" s="17"/>
-      <c r="AI24" s="17"/>
-      <c r="AJ24" s="17"/>
-      <c r="AK24" s="17"/>
-      <c r="AL24" s="17"/>
-      <c r="AM24" s="17"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="15"/>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="15">
         <f>SQRT(H13-POWER(C13,2))</f>
         <v>4.0502893415162253</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17" t="s">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="15">
         <f>ABS(E21)*(B25*SQRT(1-B29^2)*SQRT(7-3-1))/(B26*SQRT(1-B30^2))</f>
         <v>1.5264609653585459</v>
       </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17" t="s">
+      <c r="F25" s="15"/>
+      <c r="G25" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="15">
         <f>E21*(C13)/(D13)</f>
         <v>0.27978414101968369</v>
       </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
-      <c r="X25" s="17"/>
-      <c r="Y25" s="17"/>
-      <c r="Z25" s="17"/>
-      <c r="AA25" s="17"/>
-      <c r="AB25" s="17"/>
-      <c r="AC25" s="17"/>
-      <c r="AD25" s="17"/>
-      <c r="AE25" s="17"/>
-      <c r="AF25" s="17"/>
-      <c r="AG25" s="17"/>
-      <c r="AH25" s="17"/>
-      <c r="AI25" s="17"/>
-      <c r="AJ25" s="17"/>
-      <c r="AK25" s="17"/>
-      <c r="AL25" s="17"/>
-      <c r="AM25" s="17"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="15"/>
+      <c r="T25" s="15"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
+      <c r="Z25" s="15"/>
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="15"/>
+      <c r="AC25" s="15"/>
+      <c r="AD25" s="15"/>
+      <c r="AE25" s="15"/>
+      <c r="AF25" s="15"/>
+      <c r="AG25" s="15"/>
+      <c r="AH25" s="15"/>
+      <c r="AI25" s="15"/>
+      <c r="AJ25" s="15"/>
+      <c r="AK25" s="15"/>
+      <c r="AL25" s="15"/>
+      <c r="AM25" s="15"/>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="15">
         <f>SQRT(I13-POWER(D13,2))</f>
         <v>5.2160659265388842</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17" t="s">
+      <c r="C26" s="15"/>
+      <c r="D26" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="15">
         <f>3-1</f>
         <v>2</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17" t="s">
+      <c r="F26" s="15"/>
+      <c r="G26" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="15">
         <f>E20*(B24)/(B26)</f>
         <v>-0.60571582249694444</v>
       </c>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="17"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="17"/>
-      <c r="AC26" s="17"/>
-      <c r="AD26" s="17"/>
-      <c r="AE26" s="17"/>
-      <c r="AF26" s="17"/>
-      <c r="AG26" s="17"/>
-      <c r="AH26" s="17"/>
-      <c r="AI26" s="17"/>
-      <c r="AJ26" s="17"/>
-      <c r="AK26" s="17"/>
-      <c r="AL26" s="17"/>
-      <c r="AM26" s="17"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="15"/>
+      <c r="AA26" s="15"/>
+      <c r="AB26" s="15"/>
+      <c r="AC26" s="15"/>
+      <c r="AD26" s="15"/>
+      <c r="AE26" s="15"/>
+      <c r="AF26" s="15"/>
+      <c r="AG26" s="15"/>
+      <c r="AH26" s="15"/>
+      <c r="AI26" s="15"/>
+      <c r="AJ26" s="15"/>
+      <c r="AK26" s="15"/>
+      <c r="AL26" s="15"/>
+      <c r="AM26" s="15"/>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="15">
         <f>(E13-D13*B13)/(B26*B24)</f>
         <v>-0.90454003784503878</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17" t="s">
+      <c r="C27" s="15"/>
+      <c r="D27" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="15">
         <f>8-2</f>
         <v>6</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17" t="s">
+      <c r="F27" s="15"/>
+      <c r="G27" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="15">
         <f>E21*(B25)/(B26)</f>
         <v>0.41082143632498086</v>
       </c>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
-      <c r="Z27" s="17"/>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="17"/>
-      <c r="AC27" s="17"/>
-      <c r="AD27" s="17"/>
-      <c r="AE27" s="17"/>
-      <c r="AF27" s="17"/>
-      <c r="AG27" s="17"/>
-      <c r="AH27" s="17"/>
-      <c r="AI27" s="17"/>
-      <c r="AJ27" s="17"/>
-      <c r="AK27" s="17"/>
-      <c r="AL27" s="17"/>
-      <c r="AM27" s="17"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="15"/>
+      <c r="AK27" s="15"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="15">
         <f>(F13-D13*C13)/(B26*B25)</f>
         <v>0.85140836625915706</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17" t="s">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="15">
         <f>(B26^2)/(E29)*(E27)/(E26)</f>
         <v>126.6555377005613</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17" t="s">
+      <c r="F28" s="15"/>
+      <c r="G28" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="15">
         <f>(H26*B27)/B30^2</f>
         <v>0.61035078578880986</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
-      <c r="Z28" s="17"/>
-      <c r="AA28" s="17"/>
-      <c r="AB28" s="17"/>
-      <c r="AC28" s="17"/>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="17"/>
-      <c r="AF28" s="17"/>
-      <c r="AG28" s="17"/>
-      <c r="AH28" s="17"/>
-      <c r="AI28" s="17"/>
-      <c r="AJ28" s="17"/>
-      <c r="AK28" s="17"/>
-      <c r="AL28" s="17"/>
-      <c r="AM28" s="17"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+      <c r="Z28" s="15"/>
+      <c r="AA28" s="15"/>
+      <c r="AB28" s="15"/>
+      <c r="AC28" s="15"/>
+      <c r="AD28" s="15"/>
+      <c r="AE28" s="15"/>
+      <c r="AF28" s="15"/>
+      <c r="AG28" s="15"/>
+      <c r="AH28" s="15"/>
+      <c r="AI28" s="15"/>
+      <c r="AJ28" s="15"/>
+      <c r="AK28" s="15"/>
+      <c r="AL28" s="15"/>
+      <c r="AM28" s="15"/>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="15">
         <f>(J13-B13*C13)/(B25*B24)</f>
         <v>-0.72738223696707016</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17" t="s">
+      <c r="C29" s="15"/>
+      <c r="D29" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="15">
         <f>L2^2/A8</f>
         <v>0.64444107799668771</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17" t="s">
+      <c r="F29" s="15"/>
+      <c r="G29" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="15">
         <f>(H27*B28)/B30^2</f>
         <v>0.3896492142111872</v>
       </c>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="17"/>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="17"/>
-      <c r="AF29" s="17"/>
-      <c r="AG29" s="17"/>
-      <c r="AH29" s="17"/>
-      <c r="AI29" s="17"/>
-      <c r="AJ29" s="17"/>
-      <c r="AK29" s="17"/>
-      <c r="AL29" s="17"/>
-      <c r="AM29" s="17"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+      <c r="Z29" s="15"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="15"/>
+      <c r="AC29" s="15"/>
+      <c r="AD29" s="15"/>
+      <c r="AE29" s="15"/>
+      <c r="AF29" s="15"/>
+      <c r="AG29" s="15"/>
+      <c r="AH29" s="15"/>
+      <c r="AI29" s="15"/>
+      <c r="AJ29" s="15"/>
+      <c r="AK29" s="15"/>
+      <c r="AL29" s="15"/>
+      <c r="AM29" s="15"/>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="15">
         <f>SQRT((POWER(B27,2)+POWER(B28,2)-2*B27*B28*B29)/(1-POWER(B29,2)))</f>
         <v>0.94745502317018715</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
-      <c r="Z30" s="17"/>
-      <c r="AA30" s="17"/>
-      <c r="AB30" s="17"/>
-      <c r="AC30" s="17"/>
-      <c r="AD30" s="17"/>
-      <c r="AE30" s="17"/>
-      <c r="AF30" s="17"/>
-      <c r="AG30" s="17"/>
-      <c r="AH30" s="17"/>
-      <c r="AI30" s="17"/>
-      <c r="AJ30" s="17"/>
-      <c r="AK30" s="17"/>
-      <c r="AL30" s="17"/>
-      <c r="AM30" s="17"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="15"/>
+      <c r="AC30" s="15"/>
+      <c r="AD30" s="15"/>
+      <c r="AE30" s="15"/>
+      <c r="AF30" s="15"/>
+      <c r="AG30" s="15"/>
+      <c r="AH30" s="15"/>
+      <c r="AI30" s="15"/>
+      <c r="AJ30" s="15"/>
+      <c r="AK30" s="15"/>
+      <c r="AL30" s="15"/>
+      <c r="AM30" s="15"/>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="15">
         <f>B30^2</f>
         <v>0.89767102093041984</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
-      <c r="X31" s="17"/>
-      <c r="Y31" s="17"/>
-      <c r="Z31" s="17"/>
-      <c r="AA31" s="17"/>
-      <c r="AB31" s="17"/>
-      <c r="AC31" s="17"/>
-      <c r="AD31" s="17"/>
-      <c r="AE31" s="17"/>
-      <c r="AF31" s="17"/>
-      <c r="AG31" s="17"/>
-      <c r="AH31" s="17"/>
-      <c r="AI31" s="17"/>
-      <c r="AJ31" s="17"/>
-      <c r="AK31" s="17"/>
-      <c r="AL31" s="17"/>
-      <c r="AM31" s="17"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+      <c r="Z31" s="15"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="15"/>
+      <c r="AC31" s="15"/>
+      <c r="AD31" s="15"/>
+      <c r="AE31" s="15"/>
+      <c r="AF31" s="15"/>
+      <c r="AG31" s="15"/>
+      <c r="AH31" s="15"/>
+      <c r="AI31" s="15"/>
+      <c r="AJ31" s="15"/>
+      <c r="AK31" s="15"/>
+      <c r="AL31" s="15"/>
+      <c r="AM31" s="15"/>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="17"/>
-      <c r="Y32" s="17"/>
-      <c r="Z32" s="17"/>
-      <c r="AA32" s="17"/>
-      <c r="AB32" s="17"/>
-      <c r="AC32" s="17"/>
-      <c r="AD32" s="17"/>
-      <c r="AE32" s="17"/>
-      <c r="AF32" s="17"/>
-      <c r="AG32" s="17"/>
-      <c r="AH32" s="17"/>
-      <c r="AI32" s="17"/>
-      <c r="AJ32" s="17"/>
-      <c r="AK32" s="17"/>
-      <c r="AL32" s="17"/>
-      <c r="AM32" s="17"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15"/>
+      <c r="Z32" s="15"/>
+      <c r="AA32" s="15"/>
+      <c r="AB32" s="15"/>
+      <c r="AC32" s="15"/>
+      <c r="AD32" s="15"/>
+      <c r="AE32" s="15"/>
+      <c r="AF32" s="15"/>
+      <c r="AG32" s="15"/>
+      <c r="AH32" s="15"/>
+      <c r="AI32" s="15"/>
+      <c r="AJ32" s="15"/>
+      <c r="AK32" s="15"/>
+      <c r="AL32" s="15"/>
+      <c r="AM32" s="15"/>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
-      <c r="Z33" s="17"/>
-      <c r="AA33" s="17"/>
-      <c r="AB33" s="17"/>
-      <c r="AC33" s="17"/>
-      <c r="AD33" s="17"/>
-      <c r="AE33" s="17"/>
-      <c r="AF33" s="17"/>
-      <c r="AG33" s="17"/>
-      <c r="AH33" s="17"/>
-      <c r="AI33" s="17"/>
-      <c r="AJ33" s="17"/>
-      <c r="AK33" s="17"/>
-      <c r="AL33" s="17"/>
-      <c r="AM33" s="17"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
+      <c r="AC33" s="15"/>
+      <c r="AD33" s="15"/>
+      <c r="AE33" s="15"/>
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="15"/>
+      <c r="AH33" s="15"/>
+      <c r="AI33" s="15"/>
+      <c r="AJ33" s="15"/>
+      <c r="AK33" s="15"/>
+      <c r="AL33" s="15"/>
+      <c r="AM33" s="15"/>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
-      <c r="AA34" s="17"/>
-      <c r="AB34" s="17"/>
-      <c r="AC34" s="17"/>
-      <c r="AD34" s="17"/>
-      <c r="AE34" s="17"/>
-      <c r="AF34" s="17"/>
-      <c r="AG34" s="17"/>
-      <c r="AH34" s="17"/>
-      <c r="AI34" s="17"/>
-      <c r="AJ34" s="17"/>
-      <c r="AK34" s="17"/>
-      <c r="AL34" s="17"/>
-      <c r="AM34" s="17"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+      <c r="Z34" s="15"/>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="15"/>
+      <c r="AC34" s="15"/>
+      <c r="AD34" s="15"/>
+      <c r="AE34" s="15"/>
+      <c r="AF34" s="15"/>
+      <c r="AG34" s="15"/>
+      <c r="AH34" s="15"/>
+      <c r="AI34" s="15"/>
+      <c r="AJ34" s="15"/>
+      <c r="AK34" s="15"/>
+      <c r="AL34" s="15"/>
+      <c r="AM34" s="15"/>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="17"/>
-      <c r="AA35" s="17"/>
-      <c r="AB35" s="17"/>
-      <c r="AC35" s="17"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="17"/>
-      <c r="AF35" s="17"/>
-      <c r="AG35" s="17"/>
-      <c r="AH35" s="17"/>
-      <c r="AI35" s="17"/>
-      <c r="AJ35" s="17"/>
-      <c r="AK35" s="17"/>
-      <c r="AL35" s="17"/>
-      <c r="AM35" s="17"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+      <c r="Z35" s="15"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35" s="15"/>
+      <c r="AC35" s="15"/>
+      <c r="AD35" s="15"/>
+      <c r="AE35" s="15"/>
+      <c r="AF35" s="15"/>
+      <c r="AG35" s="15"/>
+      <c r="AH35" s="15"/>
+      <c r="AI35" s="15"/>
+      <c r="AJ35" s="15"/>
+      <c r="AK35" s="15"/>
+      <c r="AL35" s="15"/>
+      <c r="AM35" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A54F079-9C03-45D4-8F74-6F1D0E70EA0F}">
+  <dimension ref="A1:T98"/>
+  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.86328125" customWidth="1"/>
+    <col min="2" max="2" width="11.1328125" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" customWidth="1"/>
+    <col min="5" max="5" width="13.1328125" customWidth="1"/>
+    <col min="6" max="6" width="15.1328125" customWidth="1"/>
+    <col min="7" max="7" width="8.73046875" customWidth="1"/>
+    <col min="8" max="8" width="15.1328125" customWidth="1"/>
+    <col min="9" max="9" width="8.73046875" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="8.73046875" customWidth="1"/>
+    <col min="12" max="12" width="13.3984375" customWidth="1"/>
+    <col min="13" max="13" width="17.73046875" customWidth="1"/>
+    <col min="14" max="14" width="12.3984375" customWidth="1"/>
+    <col min="15" max="20" width="8.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="24"/>
+      <c r="E1" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="24"/>
+      <c r="I1" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="24"/>
+      <c r="K1" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="24"/>
+      <c r="M1" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="O1" s="24"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+    </row>
+    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="M2" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A3" s="31">
+        <v>1</v>
+      </c>
+      <c r="B3" s="31">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="N3" s="32">
+        <f>$B$3</f>
+        <v>141.30000000000001</v>
+      </c>
+      <c r="O3" s="32">
+        <f>B3</f>
+        <v>141.30000000000001</v>
+      </c>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+    </row>
+    <row r="4" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A4" s="31">
+        <v>2</v>
+      </c>
+      <c r="B4" s="31">
+        <v>140.5</v>
+      </c>
+      <c r="C4" s="31">
+        <f t="shared" ref="C4:C9" si="0">B4-B3</f>
+        <v>-0.80000000000001137</v>
+      </c>
+      <c r="D4" s="31">
+        <f t="shared" ref="D4:D9" si="1">B4-$B$3</f>
+        <v>-0.80000000000001137</v>
+      </c>
+      <c r="E4" s="31">
+        <f t="shared" ref="E4:E9" si="2">B4/B3</f>
+        <v>0.99433828733191787</v>
+      </c>
+      <c r="F4" s="31">
+        <f t="shared" ref="F4:F9" si="3">B4/$B$3</f>
+        <v>0.99433828733191787</v>
+      </c>
+      <c r="G4" s="32">
+        <f t="shared" ref="G4:H9" si="4">E4*100</f>
+        <v>99.433828733191788</v>
+      </c>
+      <c r="H4" s="32">
+        <f t="shared" si="4"/>
+        <v>99.433828733191788</v>
+      </c>
+      <c r="I4" s="32">
+        <f t="shared" ref="I4:J9" si="5">E4-1</f>
+        <v>-5.6617126680821306E-3</v>
+      </c>
+      <c r="J4" s="32">
+        <f t="shared" si="5"/>
+        <v>-5.6617126680821306E-3</v>
+      </c>
+      <c r="K4" s="32">
+        <f t="shared" ref="K4:L9" si="6">G4-100</f>
+        <v>-0.56617126680821173</v>
+      </c>
+      <c r="L4" s="32">
+        <f t="shared" si="6"/>
+        <v>-0.56617126680821173</v>
+      </c>
+      <c r="M4" s="32">
+        <f t="shared" ref="M4:M9" si="7">B3/100</f>
+        <v>1.413</v>
+      </c>
+      <c r="N4" s="32">
+        <f>N3+$C$11</f>
+        <v>142.58333333333334</v>
+      </c>
+      <c r="O4" s="32">
+        <f>O3*$E$11</f>
+        <v>142.5551286194451</v>
+      </c>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+    </row>
+    <row r="5" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A5" s="31">
+        <v>3</v>
+      </c>
+      <c r="B5" s="31">
+        <v>143.4</v>
+      </c>
+      <c r="C5" s="31">
+        <f t="shared" si="0"/>
+        <v>2.9000000000000057</v>
+      </c>
+      <c r="D5" s="31">
+        <f t="shared" si="1"/>
+        <v>2.0999999999999943</v>
+      </c>
+      <c r="E5" s="31">
+        <f t="shared" si="2"/>
+        <v>1.0206405693950178</v>
+      </c>
+      <c r="F5" s="31">
+        <f t="shared" si="3"/>
+        <v>1.0148619957537155</v>
+      </c>
+      <c r="G5" s="32">
+        <f t="shared" si="4"/>
+        <v>102.06405693950178</v>
+      </c>
+      <c r="H5" s="32">
+        <f t="shared" si="4"/>
+        <v>101.48619957537154</v>
+      </c>
+      <c r="I5" s="32">
+        <f t="shared" si="5"/>
+        <v>2.0640569395017794E-2</v>
+      </c>
+      <c r="J5" s="32">
+        <f t="shared" si="5"/>
+        <v>1.4861995753715496E-2</v>
+      </c>
+      <c r="K5" s="32">
+        <f t="shared" si="6"/>
+        <v>2.064056939501782</v>
+      </c>
+      <c r="L5" s="32">
+        <f t="shared" si="6"/>
+        <v>1.4861995753715433</v>
+      </c>
+      <c r="M5" s="32">
+        <f t="shared" si="7"/>
+        <v>1.405</v>
+      </c>
+      <c r="N5" s="32">
+        <f>N4+$C$11</f>
+        <v>143.86666666666667</v>
+      </c>
+      <c r="O5" s="32">
+        <f>O4*$E$11</f>
+        <v>143.82140619749848</v>
+      </c>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+    </row>
+    <row r="6" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A6" s="31">
+        <v>4</v>
+      </c>
+      <c r="B6" s="31">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="C6" s="31">
+        <f t="shared" si="0"/>
+        <v>3.4000000000000057</v>
+      </c>
+      <c r="D6" s="31">
+        <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="E6" s="31">
+        <f t="shared" si="2"/>
+        <v>1.0237099023709904</v>
+      </c>
+      <c r="F6" s="31">
+        <f t="shared" si="3"/>
+        <v>1.0389242745930645</v>
+      </c>
+      <c r="G6" s="32">
+        <f t="shared" si="4"/>
+        <v>102.37099023709904</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" si="4"/>
+        <v>103.89242745930645</v>
+      </c>
+      <c r="I6" s="32">
+        <f t="shared" si="5"/>
+        <v>2.3709902370990354E-2</v>
+      </c>
+      <c r="J6" s="32">
+        <f t="shared" si="5"/>
+        <v>3.8924274593064467E-2</v>
+      </c>
+      <c r="K6" s="32">
+        <f t="shared" si="6"/>
+        <v>2.3709902370990363</v>
+      </c>
+      <c r="L6" s="32">
+        <f t="shared" si="6"/>
+        <v>3.8924274593064467</v>
+      </c>
+      <c r="M6" s="32">
+        <f t="shared" si="7"/>
+        <v>1.4340000000000002</v>
+      </c>
+      <c r="N6" s="32">
+        <f>N5+$C$11</f>
+        <v>145.15</v>
+      </c>
+      <c r="O6" s="32">
+        <f>O5*$E$11</f>
+        <v>145.0989317672601</v>
+      </c>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A7" s="31">
+        <v>5</v>
+      </c>
+      <c r="B7" s="31">
+        <v>145</v>
+      </c>
+      <c r="C7" s="31">
+        <f t="shared" si="0"/>
+        <v>-1.8000000000000114</v>
+      </c>
+      <c r="D7" s="31">
+        <f t="shared" si="1"/>
+        <v>3.6999999999999886</v>
+      </c>
+      <c r="E7" s="31">
+        <f t="shared" si="2"/>
+        <v>0.98773841961852848</v>
+      </c>
+      <c r="F7" s="31">
+        <f t="shared" si="3"/>
+        <v>1.0261854210898795</v>
+      </c>
+      <c r="G7" s="32">
+        <f t="shared" si="4"/>
+        <v>98.773841961852852</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="4"/>
+        <v>102.61854210898795</v>
+      </c>
+      <c r="I7" s="32">
+        <f t="shared" si="5"/>
+        <v>-1.2261580381471515E-2</v>
+      </c>
+      <c r="J7" s="32">
+        <f t="shared" si="5"/>
+        <v>2.6185421089879535E-2</v>
+      </c>
+      <c r="K7" s="32">
+        <f t="shared" si="6"/>
+        <v>-1.2261580381471475</v>
+      </c>
+      <c r="L7" s="32">
+        <f t="shared" si="6"/>
+        <v>2.6185421089879526</v>
+      </c>
+      <c r="M7" s="32">
+        <f t="shared" si="7"/>
+        <v>1.4680000000000002</v>
+      </c>
+      <c r="N7" s="32">
+        <f>N6+$C$11</f>
+        <v>146.43333333333334</v>
+      </c>
+      <c r="O7" s="32">
+        <f>O6*$E$11</f>
+        <v>146.38780524151346</v>
+      </c>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+    </row>
+    <row r="8" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A8" s="31">
+        <v>6</v>
+      </c>
+      <c r="B8" s="31">
+        <v>147</v>
+      </c>
+      <c r="C8" s="31">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D8" s="31">
+        <f t="shared" si="1"/>
+        <v>5.6999999999999886</v>
+      </c>
+      <c r="E8" s="31">
+        <f t="shared" si="2"/>
+        <v>1.0137931034482759</v>
+      </c>
+      <c r="F8" s="31">
+        <f t="shared" si="3"/>
+        <v>1.0403397027600849</v>
+      </c>
+      <c r="G8" s="32">
+        <f t="shared" si="4"/>
+        <v>101.37931034482759</v>
+      </c>
+      <c r="H8" s="32">
+        <f t="shared" si="4"/>
+        <v>104.03397027600849</v>
+      </c>
+      <c r="I8" s="32">
+        <f t="shared" si="5"/>
+        <v>1.379310344827589E-2</v>
+      </c>
+      <c r="J8" s="32">
+        <f t="shared" si="5"/>
+        <v>4.0339702760084917E-2</v>
+      </c>
+      <c r="K8" s="32">
+        <f t="shared" si="6"/>
+        <v>1.3793103448275872</v>
+      </c>
+      <c r="L8" s="32">
+        <f t="shared" si="6"/>
+        <v>4.033970276008489</v>
+      </c>
+      <c r="M8" s="32">
+        <f t="shared" si="7"/>
+        <v>1.45</v>
+      </c>
+      <c r="N8" s="32">
+        <f>N7+$C$11</f>
+        <v>147.71666666666667</v>
+      </c>
+      <c r="O8" s="32">
+        <f>O7*$E$11</f>
+        <v>147.6881274205395</v>
+      </c>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A9" s="31">
+        <v>7</v>
+      </c>
+      <c r="B9" s="31">
+        <v>149</v>
+      </c>
+      <c r="C9" s="31">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D9" s="31">
+        <f t="shared" si="1"/>
+        <v>7.6999999999999886</v>
+      </c>
+      <c r="E9" s="31">
+        <f t="shared" si="2"/>
+        <v>1.0136054421768708</v>
+      </c>
+      <c r="F9" s="31">
+        <f t="shared" si="3"/>
+        <v>1.0544939844302901</v>
+      </c>
+      <c r="G9" s="32">
+        <f t="shared" si="4"/>
+        <v>101.36054421768708</v>
+      </c>
+      <c r="H9" s="32">
+        <f t="shared" si="4"/>
+        <v>105.44939844302901</v>
+      </c>
+      <c r="I9" s="32">
+        <f t="shared" si="5"/>
+        <v>1.3605442176870763E-2</v>
+      </c>
+      <c r="J9" s="32">
+        <f t="shared" si="5"/>
+        <v>5.4493984430290077E-2</v>
+      </c>
+      <c r="K9" s="32">
+        <f t="shared" si="6"/>
+        <v>1.3605442176870781</v>
+      </c>
+      <c r="L9" s="32">
+        <f t="shared" si="6"/>
+        <v>5.4493984430290112</v>
+      </c>
+      <c r="M9" s="32">
+        <f t="shared" si="7"/>
+        <v>1.47</v>
+      </c>
+      <c r="N9" s="32">
+        <f>N8+$C$11</f>
+        <v>149</v>
+      </c>
+      <c r="O9" s="32">
+        <f>O8*$E$11</f>
+        <v>149.00000000000003</v>
+      </c>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+    </row>
+    <row r="10" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A10" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="31">
+        <f>SUM(B3:B9)</f>
+        <v>1013</v>
+      </c>
+      <c r="C10" s="31">
+        <f>SUM(C3:C9)</f>
+        <v>7.6999999999999886</v>
+      </c>
+      <c r="D10" s="31">
+        <f>SUM(D3:D9)</f>
+        <v>23.899999999999949</v>
+      </c>
+      <c r="E10" s="31">
+        <f>SUM(E3:E9)</f>
+        <v>6.0538257243416016</v>
+      </c>
+      <c r="F10" s="31">
+        <f>SUM(F3:F9)</f>
+        <v>6.1691436659589529</v>
+      </c>
+      <c r="G10" s="31">
+        <f>SUM(G3:G9)</f>
+        <v>605.38257243416012</v>
+      </c>
+      <c r="H10" s="31">
+        <f>SUM(H3:H9)</f>
+        <v>616.91436659589533</v>
+      </c>
+      <c r="I10" s="31">
+        <f>SUM(I3:I9)</f>
+        <v>5.3825724341601155E-2</v>
+      </c>
+      <c r="J10" s="31">
+        <f>SUM(J3:J9)</f>
+        <v>0.16914366595895236</v>
+      </c>
+      <c r="K10" s="31">
+        <f>SUM(K3:K9)</f>
+        <v>5.3825724341601244</v>
+      </c>
+      <c r="L10" s="31">
+        <f>SUM(L3:L9)</f>
+        <v>16.914366595895231</v>
+      </c>
+      <c r="M10" s="31">
+        <f>SUM(M3:M9)</f>
+        <v>8.64</v>
+      </c>
+      <c r="N10" s="31">
+        <f>SUM(N3:N9)</f>
+        <v>1016.05</v>
+      </c>
+      <c r="O10" s="31">
+        <f>SUM(O3:O9)</f>
+        <v>1015.8513992462565</v>
+      </c>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+    </row>
+    <row r="11" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="32">
+        <f>B10/$A$38</f>
+        <v>144.71428571428572</v>
+      </c>
+      <c r="C11" s="32">
+        <f>C10/($A$38-1)</f>
+        <v>1.2833333333333314</v>
+      </c>
+      <c r="D11" s="32">
+        <f>D10/($A$38-1)</f>
+        <v>3.983333333333325</v>
+      </c>
+      <c r="E11" s="31">
+        <f>(B9/B3)^(1/(A38-1))</f>
+        <v>1.0088827220059808</v>
+      </c>
+      <c r="F11" s="31">
+        <f>SUMPRODUCT(F4:F9)^1/($A$38-1)</f>
+        <v>1.0281906109931589</v>
+      </c>
+      <c r="G11" s="32">
+        <f>G10/($A$38-1)</f>
+        <v>100.89709540569335</v>
+      </c>
+      <c r="H11" s="32">
+        <f>H10/($A$38-1)</f>
+        <v>102.81906109931589</v>
+      </c>
+      <c r="I11" s="32">
+        <f>I10/($A$38-1)</f>
+        <v>8.9709540569335253E-3</v>
+      </c>
+      <c r="J11" s="32">
+        <f>J10/($A$38-1)</f>
+        <v>2.8190610993158727E-2</v>
+      </c>
+      <c r="K11" s="32">
+        <f>K10/($A$38-1)</f>
+        <v>0.89709540569335411</v>
+      </c>
+      <c r="L11" s="32">
+        <f>L10/($A$38-1)</f>
+        <v>2.819061099315872</v>
+      </c>
+      <c r="M11" s="32">
+        <f>M10/($A$38-1)</f>
+        <v>1.4400000000000002</v>
+      </c>
+      <c r="N11" s="32">
+        <f>N10/($A$38)</f>
+        <v>145.15</v>
+      </c>
+      <c r="O11" s="32">
+        <f>O10/($A$38)</f>
+        <v>145.12162846375094</v>
+      </c>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+    </row>
+    <row r="13" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A13" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="28">
+        <f>E11*100</f>
+        <v>100.88827220059808</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A14" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="34">
+        <f>B13-100</f>
+        <v>0.88827220059808099</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+    </row>
+    <row r="16" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="28"/>
+      <c r="B16" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A17" s="28"/>
+      <c r="B17" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A18" s="28">
+        <v>1</v>
+      </c>
+      <c r="B18" s="28">
+        <v>-3</v>
+      </c>
+      <c r="C18" s="28">
+        <f t="shared" ref="C18:C24" si="8">B18^2</f>
+        <v>9</v>
+      </c>
+      <c r="D18" s="34">
+        <f>B3*B18</f>
+        <v>-423.90000000000003</v>
+      </c>
+      <c r="E18" s="34">
+        <f>$B$27+$B$28*B18</f>
+        <v>140.67500000000001</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+    </row>
+    <row r="19" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="A19" s="28">
+        <v>2</v>
+      </c>
+      <c r="B19" s="28">
+        <v>-2</v>
+      </c>
+      <c r="C19" s="28">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="D19" s="34">
+        <f>B4*B19</f>
+        <v>-281</v>
+      </c>
+      <c r="E19" s="34">
+        <f>$B$27+$B$28*B19</f>
+        <v>142.02142857142857</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+    </row>
+    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="28">
+        <v>3</v>
+      </c>
+      <c r="B20" s="28">
+        <v>-1</v>
+      </c>
+      <c r="C20" s="28">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="D20" s="34">
+        <f>B5*B20</f>
+        <v>-143.4</v>
+      </c>
+      <c r="E20" s="34">
+        <f>$B$27+$B$28*B20</f>
+        <v>143.36785714285716</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="28">
+        <v>4</v>
+      </c>
+      <c r="B21" s="28">
+        <v>0</v>
+      </c>
+      <c r="C21" s="28">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="34">
+        <f>B6*B21</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="34">
+        <f>$B$27+$B$28*B21</f>
+        <v>144.71428571428572</v>
+      </c>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="28">
+        <v>5</v>
+      </c>
+      <c r="B22" s="28">
+        <v>1</v>
+      </c>
+      <c r="C22" s="28">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="D22" s="34">
+        <f>B7*B22</f>
+        <v>145</v>
+      </c>
+      <c r="E22" s="34">
+        <f>$B$27+$B$28*B22</f>
+        <v>146.06071428571428</v>
+      </c>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="28">
+        <v>6</v>
+      </c>
+      <c r="B23" s="28">
+        <v>2</v>
+      </c>
+      <c r="C23" s="28">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="D23" s="34">
+        <f>B8*B23</f>
+        <v>294</v>
+      </c>
+      <c r="E23" s="34">
+        <f>$B$27+$B$28*B23</f>
+        <v>147.40714285714287</v>
+      </c>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="28">
+        <v>7</v>
+      </c>
+      <c r="B24" s="28">
+        <v>3</v>
+      </c>
+      <c r="C24" s="28">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="D24" s="34">
+        <f>B9*B24</f>
+        <v>447</v>
+      </c>
+      <c r="E24" s="34">
+        <f>$B$27+$B$28*B24</f>
+        <v>148.75357142857143</v>
+      </c>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="28">
+        <f>SUM(B18:B24)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="28">
+        <f>SUM(C18:C24)</f>
+        <v>28</v>
+      </c>
+      <c r="D25" s="34">
+        <f>SUM(D18:D24)</f>
+        <v>37.699999999999932</v>
+      </c>
+      <c r="E25" s="34">
+        <f>SUM(E18:E24)</f>
+        <v>1013</v>
+      </c>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="28">
+        <f>B10/A38</f>
+        <v>144.71428571428572</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="28">
+        <f>D25/C25</f>
+        <v>1.3464285714285691</v>
+      </c>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+    </row>
+    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+    </row>
+    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+    </row>
+    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+    </row>
+    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+    </row>
+    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+    </row>
+    <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="36">
+        <v>7</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+    </row>
+    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/СМіП/лабиСтатистичне_моделювання.xlsx
+++ b/СМіП/лабиСтатистичне_моделювання.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trock\Desktop\SMT\СМіП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECAD84D-0DB2-4F28-ADF1-C0115E354119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96A7491-EF53-44DF-94FF-3CFEE908C8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="5" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
   </bookViews>
@@ -20,9 +20,6 @@
     <sheet name="ЛР5" sheetId="5" r:id="rId5"/>
     <sheet name="ЛР6" sheetId="6" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -684,32 +681,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -721,10 +702,26 @@
     </xf>
     <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1734,37 +1731,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -3942,114 +3909,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Аркуш1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="A3">
-            <v>1</v>
-          </cell>
-          <cell r="B3">
-            <v>141.30000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>2</v>
-          </cell>
-          <cell r="B4">
-            <v>140.5</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>3</v>
-          </cell>
-          <cell r="B5">
-            <v>143.4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>4</v>
-          </cell>
-          <cell r="B6">
-            <v>146.80000000000001</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>5</v>
-          </cell>
-          <cell r="B7">
-            <v>145</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>6</v>
-          </cell>
-          <cell r="B8">
-            <v>147</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>7</v>
-          </cell>
-          <cell r="B9">
-            <v>149</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="E18">
-            <v>140.67500000000001</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="E19">
-            <v>142.02142857142857</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="E20">
-            <v>143.36785714285716</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21">
-            <v>144.71428571428572</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="E22">
-            <v>146.06071428571428</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="E23">
-            <v>147.40714285714287</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="E24">
-            <v>148.75357142857143</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
@@ -5699,20 +5558,20 @@
       <c r="M13" s="7"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
@@ -5898,10 +5757,10 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="21"/>
+      <c r="B24" s="35"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
@@ -5913,10 +5772,10 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="22"/>
+      <c r="B26" s="36"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
@@ -8602,1401 +8461,1401 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="23" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="24"/>
-      <c r="G1" s="25" t="s">
+      <c r="F1" s="31"/>
+      <c r="G1" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="24"/>
-      <c r="I1" s="25" t="s">
+      <c r="H1" s="31"/>
+      <c r="I1" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="24"/>
-      <c r="K1" s="26" t="s">
+      <c r="J1" s="31"/>
+      <c r="K1" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="24"/>
-      <c r="M1" s="27" t="s">
+      <c r="L1" s="31"/>
+      <c r="M1" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="24"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
     </row>
     <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="29" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N2" s="30" t="s">
+      <c r="N2" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="30" t="s">
+      <c r="O2" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
     </row>
     <row r="3" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="31">
+      <c r="A3" s="25">
         <v>1</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="25">
         <v>141.30000000000001</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="N3" s="32">
+      <c r="N3" s="26">
         <f>$B$3</f>
         <v>141.30000000000001</v>
       </c>
-      <c r="O3" s="32">
+      <c r="O3" s="26">
         <f>B3</f>
         <v>141.30000000000001</v>
       </c>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
     </row>
     <row r="4" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A4" s="31">
+      <c r="A4" s="25">
         <v>2</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="25">
         <v>140.5</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="25">
         <f t="shared" ref="C4:C9" si="0">B4-B3</f>
         <v>-0.80000000000001137</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="25">
         <f t="shared" ref="D4:D9" si="1">B4-$B$3</f>
         <v>-0.80000000000001137</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="25">
         <f t="shared" ref="E4:E9" si="2">B4/B3</f>
         <v>0.99433828733191787</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="25">
         <f t="shared" ref="F4:F9" si="3">B4/$B$3</f>
         <v>0.99433828733191787</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="26">
         <f t="shared" ref="G4:H9" si="4">E4*100</f>
         <v>99.433828733191788</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="26">
         <f t="shared" si="4"/>
         <v>99.433828733191788</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="26">
         <f t="shared" ref="I4:J9" si="5">E4-1</f>
         <v>-5.6617126680821306E-3</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="26">
         <f t="shared" si="5"/>
         <v>-5.6617126680821306E-3</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="26">
         <f t="shared" ref="K4:L9" si="6">G4-100</f>
         <v>-0.56617126680821173</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="26">
         <f t="shared" si="6"/>
         <v>-0.56617126680821173</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="26">
         <f t="shared" ref="M4:M9" si="7">B3/100</f>
         <v>1.413</v>
       </c>
-      <c r="N4" s="32">
-        <f>N3+$C$11</f>
+      <c r="N4" s="26">
+        <f t="shared" ref="N4:N9" si="8">N3+$C$11</f>
         <v>142.58333333333334</v>
       </c>
-      <c r="O4" s="32">
-        <f>O3*$E$11</f>
+      <c r="O4" s="26">
+        <f t="shared" ref="O4:O9" si="9">O3*$E$11</f>
         <v>142.5551286194451</v>
       </c>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
     </row>
     <row r="5" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A5" s="31">
+      <c r="A5" s="25">
         <v>3</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="25">
         <v>143.4</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <f t="shared" si="0"/>
         <v>2.9000000000000057</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="25">
         <f t="shared" si="1"/>
         <v>2.0999999999999943</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="25">
         <f t="shared" si="2"/>
         <v>1.0206405693950178</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="25">
         <f t="shared" si="3"/>
         <v>1.0148619957537155</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="26">
         <f t="shared" si="4"/>
         <v>102.06405693950178</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="26">
         <f t="shared" si="4"/>
         <v>101.48619957537154</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="26">
         <f t="shared" si="5"/>
         <v>2.0640569395017794E-2</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="26">
         <f t="shared" si="5"/>
         <v>1.4861995753715496E-2</v>
       </c>
-      <c r="K5" s="32">
+      <c r="K5" s="26">
         <f t="shared" si="6"/>
         <v>2.064056939501782</v>
       </c>
-      <c r="L5" s="32">
+      <c r="L5" s="26">
         <f t="shared" si="6"/>
         <v>1.4861995753715433</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5" s="26">
         <f t="shared" si="7"/>
         <v>1.405</v>
       </c>
-      <c r="N5" s="32">
-        <f>N4+$C$11</f>
+      <c r="N5" s="26">
+        <f t="shared" si="8"/>
         <v>143.86666666666667</v>
       </c>
-      <c r="O5" s="32">
-        <f>O4*$E$11</f>
+      <c r="O5" s="26">
+        <f t="shared" si="9"/>
         <v>143.82140619749848</v>
       </c>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
     </row>
     <row r="6" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A6" s="31">
+      <c r="A6" s="25">
         <v>4</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="25">
         <v>146.80000000000001</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <f t="shared" si="0"/>
         <v>3.4000000000000057</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <f t="shared" si="1"/>
         <v>5.5</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="25">
         <f t="shared" si="2"/>
         <v>1.0237099023709904</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="25">
         <f t="shared" si="3"/>
         <v>1.0389242745930645</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="26">
         <f t="shared" si="4"/>
         <v>102.37099023709904</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="26">
         <f t="shared" si="4"/>
         <v>103.89242745930645</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="26">
         <f t="shared" si="5"/>
         <v>2.3709902370990354E-2</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="26">
         <f t="shared" si="5"/>
         <v>3.8924274593064467E-2</v>
       </c>
-      <c r="K6" s="32">
+      <c r="K6" s="26">
         <f t="shared" si="6"/>
         <v>2.3709902370990363</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="26">
         <f t="shared" si="6"/>
         <v>3.8924274593064467</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="26">
         <f t="shared" si="7"/>
         <v>1.4340000000000002</v>
       </c>
-      <c r="N6" s="32">
-        <f>N5+$C$11</f>
+      <c r="N6" s="26">
+        <f t="shared" si="8"/>
         <v>145.15</v>
       </c>
-      <c r="O6" s="32">
-        <f>O5*$E$11</f>
+      <c r="O6" s="26">
+        <f t="shared" si="9"/>
         <v>145.0989317672601</v>
       </c>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
     </row>
     <row r="7" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A7" s="31">
+      <c r="A7" s="25">
         <v>5</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="25">
         <v>145</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <f t="shared" si="0"/>
         <v>-1.8000000000000114</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="25">
         <f t="shared" si="1"/>
         <v>3.6999999999999886</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <f t="shared" si="2"/>
         <v>0.98773841961852848</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="25">
         <f t="shared" si="3"/>
         <v>1.0261854210898795</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="26">
         <f t="shared" si="4"/>
         <v>98.773841961852852</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="26">
         <f t="shared" si="4"/>
         <v>102.61854210898795</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="26">
         <f t="shared" si="5"/>
         <v>-1.2261580381471515E-2</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="26">
         <f t="shared" si="5"/>
         <v>2.6185421089879535E-2</v>
       </c>
-      <c r="K7" s="32">
+      <c r="K7" s="26">
         <f t="shared" si="6"/>
         <v>-1.2261580381471475</v>
       </c>
-      <c r="L7" s="32">
+      <c r="L7" s="26">
         <f t="shared" si="6"/>
         <v>2.6185421089879526</v>
       </c>
-      <c r="M7" s="32">
+      <c r="M7" s="26">
         <f t="shared" si="7"/>
         <v>1.4680000000000002</v>
       </c>
-      <c r="N7" s="32">
-        <f>N6+$C$11</f>
+      <c r="N7" s="26">
+        <f t="shared" si="8"/>
         <v>146.43333333333334</v>
       </c>
-      <c r="O7" s="32">
-        <f>O6*$E$11</f>
+      <c r="O7" s="26">
+        <f t="shared" si="9"/>
         <v>146.38780524151346</v>
       </c>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
     </row>
     <row r="8" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A8" s="31">
+      <c r="A8" s="25">
         <v>6</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="25">
         <v>147</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="25">
         <f t="shared" si="1"/>
         <v>5.6999999999999886</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="25">
         <f t="shared" si="2"/>
         <v>1.0137931034482759</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="25">
         <f t="shared" si="3"/>
         <v>1.0403397027600849</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="26">
         <f t="shared" si="4"/>
         <v>101.37931034482759</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="26">
         <f t="shared" si="4"/>
         <v>104.03397027600849</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="26">
         <f t="shared" si="5"/>
         <v>1.379310344827589E-2</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="26">
         <f t="shared" si="5"/>
         <v>4.0339702760084917E-2</v>
       </c>
-      <c r="K8" s="32">
+      <c r="K8" s="26">
         <f t="shared" si="6"/>
         <v>1.3793103448275872</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="26">
         <f t="shared" si="6"/>
         <v>4.033970276008489</v>
       </c>
-      <c r="M8" s="32">
+      <c r="M8" s="26">
         <f t="shared" si="7"/>
         <v>1.45</v>
       </c>
-      <c r="N8" s="32">
-        <f>N7+$C$11</f>
+      <c r="N8" s="26">
+        <f t="shared" si="8"/>
         <v>147.71666666666667</v>
       </c>
-      <c r="O8" s="32">
-        <f>O7*$E$11</f>
+      <c r="O8" s="26">
+        <f t="shared" si="9"/>
         <v>147.6881274205395</v>
       </c>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
     </row>
     <row r="9" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A9" s="31">
+      <c r="A9" s="25">
         <v>7</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="25">
         <v>149</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="25">
         <f t="shared" si="1"/>
         <v>7.6999999999999886</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="25">
         <f t="shared" si="2"/>
         <v>1.0136054421768708</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="25">
         <f t="shared" si="3"/>
         <v>1.0544939844302901</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="26">
         <f t="shared" si="4"/>
         <v>101.36054421768708</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="26">
         <f t="shared" si="4"/>
         <v>105.44939844302901</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="26">
         <f t="shared" si="5"/>
         <v>1.3605442176870763E-2</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="26">
         <f t="shared" si="5"/>
         <v>5.4493984430290077E-2</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="26">
         <f t="shared" si="6"/>
         <v>1.3605442176870781</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="26">
         <f t="shared" si="6"/>
         <v>5.4493984430290112</v>
       </c>
-      <c r="M9" s="32">
+      <c r="M9" s="26">
         <f t="shared" si="7"/>
         <v>1.47</v>
       </c>
-      <c r="N9" s="32">
-        <f>N8+$C$11</f>
+      <c r="N9" s="26">
+        <f t="shared" si="8"/>
         <v>149</v>
       </c>
-      <c r="O9" s="32">
-        <f>O8*$E$11</f>
+      <c r="O9" s="26">
+        <f t="shared" si="9"/>
         <v>149.00000000000003</v>
       </c>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
     </row>
     <row r="10" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="31">
-        <f>SUM(B3:B9)</f>
+      <c r="B10" s="25">
+        <f t="shared" ref="B10:O10" si="10">SUM(B3:B9)</f>
         <v>1013</v>
       </c>
-      <c r="C10" s="31">
-        <f>SUM(C3:C9)</f>
+      <c r="C10" s="25">
+        <f t="shared" si="10"/>
         <v>7.6999999999999886</v>
       </c>
-      <c r="D10" s="31">
-        <f>SUM(D3:D9)</f>
+      <c r="D10" s="25">
+        <f t="shared" si="10"/>
         <v>23.899999999999949</v>
       </c>
-      <c r="E10" s="31">
-        <f>SUM(E3:E9)</f>
+      <c r="E10" s="25">
+        <f t="shared" si="10"/>
         <v>6.0538257243416016</v>
       </c>
-      <c r="F10" s="31">
-        <f>SUM(F3:F9)</f>
+      <c r="F10" s="25">
+        <f t="shared" si="10"/>
         <v>6.1691436659589529</v>
       </c>
-      <c r="G10" s="31">
-        <f>SUM(G3:G9)</f>
+      <c r="G10" s="25">
+        <f t="shared" si="10"/>
         <v>605.38257243416012</v>
       </c>
-      <c r="H10" s="31">
-        <f>SUM(H3:H9)</f>
+      <c r="H10" s="25">
+        <f t="shared" si="10"/>
         <v>616.91436659589533</v>
       </c>
-      <c r="I10" s="31">
-        <f>SUM(I3:I9)</f>
+      <c r="I10" s="25">
+        <f t="shared" si="10"/>
         <v>5.3825724341601155E-2</v>
       </c>
-      <c r="J10" s="31">
-        <f>SUM(J3:J9)</f>
+      <c r="J10" s="25">
+        <f t="shared" si="10"/>
         <v>0.16914366595895236</v>
       </c>
-      <c r="K10" s="31">
-        <f>SUM(K3:K9)</f>
+      <c r="K10" s="25">
+        <f t="shared" si="10"/>
         <v>5.3825724341601244</v>
       </c>
-      <c r="L10" s="31">
-        <f>SUM(L3:L9)</f>
+      <c r="L10" s="25">
+        <f t="shared" si="10"/>
         <v>16.914366595895231</v>
       </c>
-      <c r="M10" s="31">
-        <f>SUM(M3:M9)</f>
+      <c r="M10" s="25">
+        <f t="shared" si="10"/>
         <v>8.64</v>
       </c>
-      <c r="N10" s="31">
-        <f>SUM(N3:N9)</f>
+      <c r="N10" s="25">
+        <f t="shared" si="10"/>
         <v>1016.05</v>
       </c>
-      <c r="O10" s="31">
-        <f>SUM(O3:O9)</f>
+      <c r="O10" s="25">
+        <f t="shared" si="10"/>
         <v>1015.8513992462565</v>
       </c>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
     </row>
     <row r="11" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="26">
         <f>B10/$A$38</f>
         <v>144.71428571428572</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="26">
         <f>C10/($A$38-1)</f>
         <v>1.2833333333333314</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="26">
         <f>D10/($A$38-1)</f>
         <v>3.983333333333325</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="25">
         <f>(B9/B3)^(1/(A38-1))</f>
         <v>1.0088827220059808</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="25">
         <f>SUMPRODUCT(F4:F9)^1/($A$38-1)</f>
         <v>1.0281906109931589</v>
       </c>
-      <c r="G11" s="32">
-        <f>G10/($A$38-1)</f>
+      <c r="G11" s="26">
+        <f t="shared" ref="G11:M11" si="11">G10/($A$38-1)</f>
         <v>100.89709540569335</v>
       </c>
-      <c r="H11" s="32">
-        <f>H10/($A$38-1)</f>
+      <c r="H11" s="26">
+        <f t="shared" si="11"/>
         <v>102.81906109931589</v>
       </c>
-      <c r="I11" s="32">
-        <f>I10/($A$38-1)</f>
+      <c r="I11" s="26">
+        <f t="shared" si="11"/>
         <v>8.9709540569335253E-3</v>
       </c>
-      <c r="J11" s="32">
-        <f>J10/($A$38-1)</f>
+      <c r="J11" s="26">
+        <f t="shared" si="11"/>
         <v>2.8190610993158727E-2</v>
       </c>
-      <c r="K11" s="32">
-        <f>K10/($A$38-1)</f>
+      <c r="K11" s="26">
+        <f t="shared" si="11"/>
         <v>0.89709540569335411</v>
       </c>
-      <c r="L11" s="32">
-        <f>L10/($A$38-1)</f>
+      <c r="L11" s="26">
+        <f t="shared" si="11"/>
         <v>2.819061099315872</v>
       </c>
-      <c r="M11" s="32">
-        <f>M10/($A$38-1)</f>
+      <c r="M11" s="26">
+        <f t="shared" si="11"/>
         <v>1.4400000000000002</v>
       </c>
-      <c r="N11" s="32">
+      <c r="N11" s="26">
         <f>N10/($A$38)</f>
         <v>145.15</v>
       </c>
-      <c r="O11" s="32">
+      <c r="O11" s="26">
         <f>O10/($A$38)</f>
         <v>145.12162846375094</v>
       </c>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="28"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
     </row>
     <row r="12" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="28"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
     </row>
     <row r="13" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="24">
         <f>E11*100</f>
         <v>100.88827220059808</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
     </row>
     <row r="14" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="28">
         <f>B13-100</f>
         <v>0.88827220059808099</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="28"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
     </row>
     <row r="15" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
     </row>
     <row r="16" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="28"/>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
     </row>
     <row r="17" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="28"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
     </row>
     <row r="18" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A18" s="28">
+      <c r="A18" s="24">
         <v>1</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="24">
         <v>-3</v>
       </c>
-      <c r="C18" s="28">
-        <f t="shared" ref="C18:C24" si="8">B18^2</f>
+      <c r="C18" s="24">
+        <f t="shared" ref="C18:C24" si="12">B18^2</f>
         <v>9</v>
       </c>
-      <c r="D18" s="34">
-        <f>B3*B18</f>
+      <c r="D18" s="28">
+        <f t="shared" ref="D18:D24" si="13">B3*B18</f>
         <v>-423.90000000000003</v>
       </c>
-      <c r="E18" s="34">
-        <f>$B$27+$B$28*B18</f>
+      <c r="E18" s="28">
+        <f t="shared" ref="E18:E24" si="14">$B$27+$B$28*B18</f>
         <v>140.67500000000001</v>
       </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24"/>
     </row>
     <row r="19" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A19" s="28">
+      <c r="A19" s="24">
         <v>2</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="24">
         <v>-2</v>
       </c>
-      <c r="C19" s="28">
-        <f t="shared" si="8"/>
+      <c r="C19" s="24">
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="D19" s="34">
-        <f>B4*B19</f>
+      <c r="D19" s="28">
+        <f t="shared" si="13"/>
         <v>-281</v>
       </c>
-      <c r="E19" s="34">
-        <f>$B$27+$B$28*B19</f>
+      <c r="E19" s="28">
+        <f t="shared" si="14"/>
         <v>142.02142857142857</v>
       </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="28">
+      <c r="A20" s="24">
         <v>3</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="24">
         <v>-1</v>
       </c>
-      <c r="C20" s="28">
-        <f t="shared" si="8"/>
+      <c r="C20" s="24">
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="D20" s="34">
-        <f>B5*B20</f>
+      <c r="D20" s="28">
+        <f t="shared" si="13"/>
         <v>-143.4</v>
       </c>
-      <c r="E20" s="34">
-        <f>$B$27+$B$28*B20</f>
+      <c r="E20" s="28">
+        <f t="shared" si="14"/>
         <v>143.36785714285716</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="24"/>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="28">
+      <c r="A21" s="24">
         <v>4</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="24">
         <v>0</v>
       </c>
-      <c r="C21" s="28">
-        <f t="shared" si="8"/>
+      <c r="C21" s="24">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="D21" s="34">
-        <f>B6*B21</f>
+      <c r="D21" s="28">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="E21" s="34">
-        <f>$B$27+$B$28*B21</f>
+      <c r="E21" s="28">
+        <f t="shared" si="14"/>
         <v>144.71428571428572</v>
       </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="24"/>
+      <c r="T21" s="24"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28">
+      <c r="A22" s="24">
         <v>5</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="24">
         <v>1</v>
       </c>
-      <c r="C22" s="28">
-        <f t="shared" si="8"/>
+      <c r="C22" s="24">
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="D22" s="34">
-        <f>B7*B22</f>
+      <c r="D22" s="28">
+        <f t="shared" si="13"/>
         <v>145</v>
       </c>
-      <c r="E22" s="34">
-        <f>$B$27+$B$28*B22</f>
+      <c r="E22" s="28">
+        <f t="shared" si="14"/>
         <v>146.06071428571428</v>
       </c>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="24"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="28">
+      <c r="A23" s="24">
         <v>6</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="24">
         <v>2</v>
       </c>
-      <c r="C23" s="28">
-        <f t="shared" si="8"/>
+      <c r="C23" s="24">
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="D23" s="34">
-        <f>B8*B23</f>
+      <c r="D23" s="28">
+        <f t="shared" si="13"/>
         <v>294</v>
       </c>
-      <c r="E23" s="34">
-        <f>$B$27+$B$28*B23</f>
+      <c r="E23" s="28">
+        <f t="shared" si="14"/>
         <v>147.40714285714287</v>
       </c>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="24"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="28">
+      <c r="A24" s="24">
         <v>7</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="24">
         <v>3</v>
       </c>
-      <c r="C24" s="28">
-        <f t="shared" si="8"/>
+      <c r="C24" s="24">
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
-      <c r="D24" s="34">
-        <f>B9*B24</f>
+      <c r="D24" s="28">
+        <f t="shared" si="13"/>
         <v>447</v>
       </c>
-      <c r="E24" s="34">
-        <f>$B$27+$B$28*B24</f>
+      <c r="E24" s="28">
+        <f t="shared" si="14"/>
         <v>148.75357142857143</v>
       </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="24"/>
+      <c r="T24" s="24"/>
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="24">
         <f>SUM(B18:B24)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="24">
         <f>SUM(C18:C24)</f>
         <v>28</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="28">
         <f>SUM(D18:D24)</f>
         <v>37.699999999999932</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="28">
         <f>SUM(E18:E24)</f>
         <v>1013</v>
       </c>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
     </row>
     <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="24">
         <f>B10/A38</f>
         <v>144.71428571428572</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="24"/>
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="24">
         <f>D25/C25</f>
         <v>1.3464285714285691</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="24"/>
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="24"/>
+      <c r="T29" s="24"/>
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="28"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="28"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="24"/>
+      <c r="S30" s="24"/>
+      <c r="T30" s="24"/>
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
+      <c r="S31" s="24"/>
+      <c r="T31" s="24"/>
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="24"/>
+      <c r="S32" s="24"/>
+      <c r="T32" s="24"/>
     </row>
     <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
+      <c r="R33" s="24"/>
+      <c r="S33" s="24"/>
+      <c r="T33" s="24"/>
     </row>
     <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="24"/>
+      <c r="T34" s="24"/>
     </row>
     <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
     </row>
     <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="24"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="24"/>
+      <c r="R36" s="24"/>
+      <c r="S36" s="24"/>
+      <c r="T36" s="24"/>
     </row>
     <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="24"/>
+      <c r="R37" s="24"/>
+      <c r="S37" s="24"/>
+      <c r="T37" s="24"/>
     </row>
     <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="36">
+      <c r="A38" s="29">
         <v>7</v>
       </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="24"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="24"/>
     </row>
     <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>

--- a/СМіП/лабиСтатистичне_моделювання.xlsx
+++ b/СМіП/лабиСтатистичне_моделювання.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trock\Desktop\SMT\СМіП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96A7491-EF53-44DF-94FF-3CFEE908C8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD07314C-AC42-4966-9901-37E634B4D1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="5" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ЛР1" sheetId="1" r:id="rId1"/>

--- a/СМіП/лабиСтатистичне_моделювання.xlsx
+++ b/СМіП/лабиСтатистичне_моделювання.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trock\Desktop\SMT\СМіП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SMT\СМіП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD07314C-AC42-4966-9901-37E634B4D1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA38CBEA-6513-45C0-8616-304C0CE11FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
+    <workbookView xWindow="-28920" yWindow="5970" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ЛР1" sheetId="1" r:id="rId1"/>
@@ -34,19 +34,22 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -592,24 +595,34 @@
       <sz val="12"/>
       <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -704,6 +717,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -717,16 +736,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
+    <cellStyle name="Відсотковий" xfId="1" builtinId="5"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -744,7 +757,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
+  <c:lang val="uk-UA"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -810,7 +823,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="uk-UA"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1115,7 +1128,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="309470944"/>
@@ -1178,7 +1191,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="309477184"/>
@@ -1230,13 +1243,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="uk-UA"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1244,6 +1256,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1267,7 +1280,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
+      <a:endParaRPr lang="uk-UA"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1281,7 +1294,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
+  <c:lang val="uk-UA"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1594,7 +1607,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1660592592"/>
@@ -1658,7 +1671,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1660594992"/>
@@ -1675,7 +1688,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1683,6 +1695,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1706,7 +1719,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
+      <a:endParaRPr lang="uk-UA"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1720,7 +1733,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
+  <c:lang val="uk-UA"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1997,7 +2010,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1101488048"/>
@@ -2059,7 +2072,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1101487088"/>
@@ -2076,7 +2089,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2084,6 +2096,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2107,7 +2120,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
+      <a:endParaRPr lang="uk-UA"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3912,7 +3925,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Офіс">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3950,7 +3963,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Офіс">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4056,7 +4069,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Офіс">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4207,9 +4220,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1856120-CB05-46AC-BC44-ECB9379177B5}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4236,7 +4249,7 @@
         <v>2.1769230769230772</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4267,7 +4280,7 @@
         <v>46.42307692307692</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4294,7 +4307,7 @@
         <v>1.4959171597633161</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4321,7 +4334,7 @@
         <v>0.90982248520709408</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4348,7 +4361,7 @@
         <v>8.725207100591696</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4375,7 +4388,7 @@
         <v>1.2786390532544409</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4402,7 +4415,7 @@
         <v>3.4940236686390485</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4429,7 +4442,7 @@
         <v>9.4674556213017083E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4456,7 +4469,7 @@
         <v>0.23485207100591377</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4483,7 +4496,7 @@
         <v>1.7914792899408443</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <f>SUM(B2:B10)</f>
         <v>35</v>
@@ -4517,9 +4530,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB0876DF-9524-4501-8B6C-7EB698F79759}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -4545,7 +4558,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4590,7 +4603,7 @@
         <v>0.93414094602397701</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4635,7 +4648,7 @@
         <v>0.87261930703857027</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4673,7 +4686,7 @@
         <v>47.95338294414497</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4711,7 +4724,7 @@
         <v>1.4901385239342084</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4753,7 +4766,7 @@
         <v>0.15423544067268763</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4791,7 +4804,7 @@
         <v>82.424495884186641</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4829,7 +4842,7 @@
         <v>6.924838116818691</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4866,7 +4879,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4897,7 +4910,7 @@
         <v>1.960000000000016</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -4926,7 +4939,7 @@
         <v>493.99999999999989</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -4959,17 +4972,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01BFC95-FB62-454A-8DFD-E6026B23C1F3}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -5010,7 +5023,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -5061,7 +5074,7 @@
         <v>497213.12955222564</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -5112,7 +5125,7 @@
         <v>273420.27683704928</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -5163,7 +5176,7 @@
         <v>125223.51660345681</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -5214,7 +5227,7 @@
         <v>22216.005175360388</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -5265,7 +5278,7 @@
         <v>3074.4754776926429</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -5316,7 +5329,7 @@
         <v>51041.240178272099</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -5367,7 +5380,7 @@
         <v>132540.58509537828</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -5418,7 +5431,7 @@
         <v>316847.90630395117</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -5469,7 +5482,7 @@
         <v>401348.01879626035</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -5484,7 +5497,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>34</v>
       </c>
@@ -5537,7 +5550,7 @@
         <v>1822925.1540196468</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>35</v>
       </c>
@@ -5557,23 +5570,23 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="35" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f>$C$12</f>
         <v>14724</v>
@@ -5615,7 +5628,7 @@
         <v>12.425300000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <f>$G$12</f>
         <v>17871.77</v>
@@ -5657,7 +5670,7 @@
         <v>16.938029</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f>$H$12</f>
         <v>23824.349900000005</v>
@@ -5699,7 +5712,7 @@
         <v>24.819190610000007</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -5715,7 +5728,7 @@
         <v>-714.69362941446605</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -5731,7 +5744,7 @@
         <v>3125.7484879169415</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -5747,7 +5760,7 @@
         <v>-815.47324405191284</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -5756,13 +5769,13 @@
         <v>-1312.1030221199583</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" s="35" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="35"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B24" s="30"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -5771,13 +5784,13 @@
         <v>0.98829366545865538</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" s="36" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="36"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B26" s="31"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -5786,7 +5799,7 @@
         <v>8.2291781925914204E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -5809,12 +5822,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C892A349-E08C-4EF9-852D-1395A2DE412E}">
   <dimension ref="A1:Z19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="10.3984375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5855,7 +5868,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5903,7 +5916,7 @@
         <v>43.133388144978369</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5941,7 +5954,7 @@
         <v>33.585469199230083</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5979,7 +5992,7 @@
         <v>29.133759613733172</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6017,7 +6030,7 @@
         <v>35.049563985434901</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6055,7 +6068,7 @@
         <v>34.327235344009537</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6093,7 +6106,7 @@
         <v>30.204850598711925</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6131,7 +6144,7 @@
         <v>21.311169892708786</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6169,7 +6182,7 @@
         <v>23.311883461595887</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -6210,7 +6223,7 @@
         <v>241.1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="L12">
         <v>8</v>
       </c>
@@ -6248,7 +6261,7 @@
         <v>241.1</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="L13">
         <v>127.5</v>
       </c>
@@ -6286,7 +6299,7 @@
         <v>3986.43</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="L14">
         <v>112.6</v>
       </c>
@@ -6324,7 +6337,7 @@
         <v>3315.15</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="L16" t="s">
         <v>37</v>
       </c>
@@ -6333,7 +6346,7 @@
         <v>17035.187800000309</v>
       </c>
     </row>
-    <row r="17" spans="12:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L17" t="s">
         <v>59</v>
       </c>
@@ -6349,7 +6362,7 @@
         <v>43.133388144977403</v>
       </c>
     </row>
-    <row r="18" spans="12:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L18" t="s">
         <v>60</v>
       </c>
@@ -6365,7 +6378,7 @@
         <v>0.52906632470468085</v>
       </c>
     </row>
-    <row r="19" spans="12:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="12:16" x14ac:dyDescent="0.25">
       <c r="L19" t="s">
         <v>61</v>
       </c>
@@ -6394,9 +6407,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C4660E-B09C-4B66-8E8A-7F5AFFC18A2A}">
   <dimension ref="A1:AM35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:39" ht="81" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:39" ht="85.5" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
@@ -6461,7 +6474,7 @@
       <c r="AL1" s="15"/>
       <c r="AM1" s="15"/>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -6534,7 +6547,7 @@
       <c r="AL2" s="15"/>
       <c r="AM2" s="15"/>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -6607,7 +6620,7 @@
       <c r="AL3" s="15"/>
       <c r="AM3" s="15"/>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -6680,7 +6693,7 @@
       <c r="AL4" s="15"/>
       <c r="AM4" s="15"/>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -6753,7 +6766,7 @@
       <c r="AL5" s="15"/>
       <c r="AM5" s="15"/>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -6826,7 +6839,7 @@
       <c r="AL6" s="15"/>
       <c r="AM6" s="15"/>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -6899,7 +6912,7 @@
       <c r="AL7" s="15"/>
       <c r="AM7" s="15"/>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -6972,7 +6985,7 @@
       <c r="AL8" s="15"/>
       <c r="AM8" s="15"/>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -7045,7 +7058,7 @@
       <c r="AL9" s="15"/>
       <c r="AM9" s="15"/>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -7086,7 +7099,7 @@
       <c r="AL10" s="15"/>
       <c r="AM10" s="15"/>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -7127,7 +7140,7 @@
       <c r="AL11" s="15"/>
       <c r="AM11" s="15"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -7203,7 +7216,7 @@
       <c r="AL12" s="15"/>
       <c r="AM12" s="15"/>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>74</v>
       </c>
@@ -7279,7 +7292,7 @@
       <c r="AL13" s="15"/>
       <c r="AM13" s="15"/>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -7320,7 +7333,7 @@
       <c r="AL14" s="15"/>
       <c r="AM14" s="15"/>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <f>$D$12</f>
         <v>241.1</v>
@@ -7400,7 +7413,7 @@
       <c r="AL15" s="15"/>
       <c r="AM15" s="15"/>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <f>$E$12</f>
         <v>3315.15</v>
@@ -7480,7 +7493,7 @@
       <c r="AL16" s="15"/>
       <c r="AM16" s="15"/>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <f>$F$12</f>
         <v>3986.43</v>
@@ -7560,7 +7573,7 @@
       <c r="AL17" s="15"/>
       <c r="AM17" s="15"/>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -7601,7 +7614,7 @@
       <c r="AL18" s="15"/>
       <c r="AM18" s="15"/>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>37</v>
       </c>
@@ -7652,7 +7665,7 @@
       <c r="AL19" s="15"/>
       <c r="AM19" s="15"/>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>41</v>
       </c>
@@ -7703,7 +7716,7 @@
       <c r="AL20" s="15"/>
       <c r="AM20" s="15"/>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>43</v>
       </c>
@@ -7754,7 +7767,7 @@
       <c r="AL21" s="15"/>
       <c r="AM21" s="15"/>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>75</v>
       </c>
@@ -7800,7 +7813,7 @@
       <c r="AL22" s="15"/>
       <c r="AM22" s="15"/>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -7841,7 +7854,7 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="15"/>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>76</v>
       </c>
@@ -7897,7 +7910,7 @@
       <c r="AL24" s="15"/>
       <c r="AM24" s="15"/>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>78</v>
       </c>
@@ -7953,7 +7966,7 @@
       <c r="AL25" s="15"/>
       <c r="AM25" s="15"/>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>81</v>
       </c>
@@ -8009,7 +8022,7 @@
       <c r="AL26" s="15"/>
       <c r="AM26" s="15"/>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>84</v>
       </c>
@@ -8065,7 +8078,7 @@
       <c r="AL27" s="15"/>
       <c r="AM27" s="15"/>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>87</v>
       </c>
@@ -8121,7 +8134,7 @@
       <c r="AL28" s="15"/>
       <c r="AM28" s="15"/>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>90</v>
       </c>
@@ -8177,7 +8190,7 @@
       <c r="AL29" s="15"/>
       <c r="AM29" s="15"/>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>93</v>
       </c>
@@ -8223,7 +8236,7 @@
       <c r="AL30" s="15"/>
       <c r="AM30" s="15"/>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>23</v>
       </c>
@@ -8269,7 +8282,7 @@
       <c r="AL31" s="15"/>
       <c r="AM31" s="15"/>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -8310,7 +8323,7 @@
       <c r="AL32" s="15"/>
       <c r="AM32" s="15"/>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -8351,7 +8364,7 @@
       <c r="AL33" s="15"/>
       <c r="AM33" s="15"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -8392,7 +8405,7 @@
       <c r="AL34" s="15"/>
       <c r="AM34" s="15"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -8441,68 +8454,68 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A54F079-9C03-45D4-8F74-6F1D0E70EA0F}">
   <dimension ref="A1:T98"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" customWidth="1"/>
-    <col min="2" max="2" width="11.1328125" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" customWidth="1"/>
-    <col min="5" max="5" width="13.1328125" customWidth="1"/>
-    <col min="6" max="6" width="15.1328125" customWidth="1"/>
-    <col min="7" max="7" width="8.73046875" customWidth="1"/>
-    <col min="8" max="8" width="15.1328125" customWidth="1"/>
-    <col min="9" max="9" width="8.73046875" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="8.73046875" customWidth="1"/>
-    <col min="12" max="12" width="13.3984375" customWidth="1"/>
-    <col min="13" max="13" width="17.73046875" customWidth="1"/>
-    <col min="14" max="14" width="12.3984375" customWidth="1"/>
-    <col min="15" max="20" width="8.73046875" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" customWidth="1"/>
+    <col min="15" max="20" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="33" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="31"/>
-      <c r="G1" s="34" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="34" t="s">
+      <c r="H1" s="33"/>
+      <c r="I1" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="30" t="s">
+      <c r="J1" s="33"/>
+      <c r="K1" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="31"/>
+      <c r="L1" s="33"/>
       <c r="M1" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="31"/>
+      <c r="O1" s="33"/>
       <c r="P1" s="24"/>
       <c r="Q1" s="24"/>
       <c r="R1" s="24"/>
       <c r="S1" s="24"/>
       <c r="T1" s="24"/>
     </row>
-    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
+    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="21" t="s">
         <v>104</v>
       </c>
@@ -8548,7 +8561,7 @@
       <c r="S2" s="24"/>
       <c r="T2" s="24"/>
     </row>
-    <row r="3" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="25">
         <v>1</v>
       </c>
@@ -8602,7 +8615,7 @@
       <c r="S3" s="24"/>
       <c r="T3" s="24"/>
     </row>
-    <row r="4" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>2</v>
       </c>
@@ -8667,7 +8680,7 @@
       <c r="S4" s="24"/>
       <c r="T4" s="24"/>
     </row>
-    <row r="5" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="25">
         <v>3</v>
       </c>
@@ -8732,7 +8745,7 @@
       <c r="S5" s="24"/>
       <c r="T5" s="24"/>
     </row>
-    <row r="6" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>4</v>
       </c>
@@ -8797,7 +8810,7 @@
       <c r="S6" s="24"/>
       <c r="T6" s="24"/>
     </row>
-    <row r="7" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="25">
         <v>5</v>
       </c>
@@ -8862,7 +8875,7 @@
       <c r="S7" s="24"/>
       <c r="T7" s="24"/>
     </row>
-    <row r="8" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <v>6</v>
       </c>
@@ -8927,7 +8940,7 @@
       <c r="S8" s="24"/>
       <c r="T8" s="24"/>
     </row>
-    <row r="9" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="25">
         <v>7</v>
       </c>
@@ -8992,7 +9005,7 @@
       <c r="S9" s="24"/>
       <c r="T9" s="24"/>
     </row>
-    <row r="10" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>73</v>
       </c>
@@ -9058,7 +9071,7 @@
       <c r="S10" s="24"/>
       <c r="T10" s="24"/>
     </row>
-    <row r="11" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>108</v>
       </c>
@@ -9124,7 +9137,7 @@
       <c r="S11" s="24"/>
       <c r="T11" s="24"/>
     </row>
-    <row r="12" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="24"/>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -9146,7 +9159,7 @@
       <c r="S12" s="24"/>
       <c r="T12" s="24"/>
     </row>
-    <row r="13" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
         <v>109</v>
       </c>
@@ -9173,7 +9186,7 @@
       <c r="S13" s="24"/>
       <c r="T13" s="24"/>
     </row>
-    <row r="14" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
         <v>110</v>
       </c>
@@ -9200,7 +9213,7 @@
       <c r="S14" s="24"/>
       <c r="T14" s="24"/>
     </row>
-    <row r="15" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="24"/>
       <c r="B15" s="24"/>
       <c r="C15" s="24"/>
@@ -9222,15 +9235,15 @@
       <c r="S15" s="24"/>
       <c r="T15" s="24"/>
     </row>
-    <row r="16" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="24"/>
@@ -9246,7 +9259,7 @@
       <c r="S16" s="24"/>
       <c r="T16" s="24"/>
     </row>
-    <row r="17" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="24"/>
       <c r="B17" s="24" t="s">
         <v>112</v>
@@ -9276,7 +9289,7 @@
       <c r="S17" s="24"/>
       <c r="T17" s="24"/>
     </row>
-    <row r="18" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <v>1</v>
       </c>
@@ -9311,7 +9324,7 @@
       <c r="S18" s="24"/>
       <c r="T18" s="24"/>
     </row>
-    <row r="19" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <v>2</v>
       </c>
@@ -9346,7 +9359,7 @@
       <c r="S19" s="24"/>
       <c r="T19" s="24"/>
     </row>
-    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
         <v>3</v>
       </c>
@@ -9381,7 +9394,7 @@
       <c r="S20" s="24"/>
       <c r="T20" s="24"/>
     </row>
-    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
         <v>4</v>
       </c>
@@ -9416,7 +9429,7 @@
       <c r="S21" s="24"/>
       <c r="T21" s="24"/>
     </row>
-    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="24">
         <v>5</v>
       </c>
@@ -9451,7 +9464,7 @@
       <c r="S22" s="24"/>
       <c r="T22" s="24"/>
     </row>
-    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
         <v>6</v>
       </c>
@@ -9486,7 +9499,7 @@
       <c r="S23" s="24"/>
       <c r="T23" s="24"/>
     </row>
-    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24">
         <v>7</v>
       </c>
@@ -9521,7 +9534,7 @@
       <c r="S24" s="24"/>
       <c r="T24" s="24"/>
     </row>
-    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
         <v>73</v>
       </c>
@@ -9557,7 +9570,7 @@
       <c r="S25" s="24"/>
       <c r="T25" s="24"/>
     </row>
-    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24"/>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
@@ -9579,7 +9592,7 @@
       <c r="S26" s="24"/>
       <c r="T26" s="24"/>
     </row>
-    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
         <v>15</v>
       </c>
@@ -9606,7 +9619,7 @@
       <c r="S27" s="24"/>
       <c r="T27" s="24"/>
     </row>
-    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
         <v>16</v>
       </c>
@@ -9633,7 +9646,7 @@
       <c r="S28" s="24"/>
       <c r="T28" s="24"/>
     </row>
-    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -9655,7 +9668,7 @@
       <c r="S29" s="24"/>
       <c r="T29" s="24"/>
     </row>
-    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="24"/>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
@@ -9677,7 +9690,7 @@
       <c r="S30" s="24"/>
       <c r="T30" s="24"/>
     </row>
-    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="24"/>
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
@@ -9699,7 +9712,7 @@
       <c r="S31" s="24"/>
       <c r="T31" s="24"/>
     </row>
-    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -9721,7 +9734,7 @@
       <c r="S32" s="24"/>
       <c r="T32" s="24"/>
     </row>
-    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
@@ -9743,7 +9756,7 @@
       <c r="S33" s="24"/>
       <c r="T33" s="24"/>
     </row>
-    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
@@ -9765,7 +9778,7 @@
       <c r="S34" s="24"/>
       <c r="T34" s="24"/>
     </row>
-    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
@@ -9787,7 +9800,7 @@
       <c r="S35" s="24"/>
       <c r="T35" s="24"/>
     </row>
-    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -9809,7 +9822,7 @@
       <c r="S36" s="24"/>
       <c r="T36" s="24"/>
     </row>
-    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>114</v>
       </c>
@@ -9833,7 +9846,7 @@
       <c r="S37" s="24"/>
       <c r="T37" s="24"/>
     </row>
-    <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="29">
         <v>7</v>
       </c>
@@ -9857,66 +9870,66 @@
       <c r="S38" s="24"/>
       <c r="T38" s="24"/>
     </row>
-    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="K1:L1"/>

--- a/СМіП/лабиСтатистичне_моделювання.xlsx
+++ b/СМіП/лабиСтатистичне_моделювання.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SMT\СМіП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trock\Desktop\SMT\СМіП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA38CBEA-6513-45C0-8616-304C0CE11FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB8A6F-D920-410E-9D7B-6DF895646BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5970" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="5" xr2:uid="{C6454709-9D82-4E43-897D-8CDF4628B8E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ЛР1" sheetId="1" r:id="rId1"/>
@@ -34,22 +34,19 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -717,12 +714,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -736,10 +727,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Відсотковий" xfId="1" builtinId="5"/>
-    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -757,7 +754,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="uk-UA"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1249,6 +1246,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1256,7 +1254,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1294,7 +1291,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="uk-UA"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1688,6 +1685,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1695,7 +1693,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1733,7 +1730,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="uk-UA"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2089,6 +2086,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2096,7 +2094,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3925,7 +3922,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Офіс">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3963,7 +3960,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Офіс">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4069,7 +4066,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Офіс">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4220,9 +4217,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1856120-CB05-46AC-BC44-ECB9379177B5}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4249,7 +4246,7 @@
         <v>2.1769230769230772</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4280,7 +4277,7 @@
         <v>46.42307692307692</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4307,7 +4304,7 @@
         <v>1.4959171597633161</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4334,7 +4331,7 @@
         <v>0.90982248520709408</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4361,7 +4358,7 @@
         <v>8.725207100591696</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4388,7 +4385,7 @@
         <v>1.2786390532544409</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4415,7 +4412,7 @@
         <v>3.4940236686390485</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4442,7 +4439,7 @@
         <v>9.4674556213017083E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4469,7 +4466,7 @@
         <v>0.23485207100591377</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4496,7 +4493,7 @@
         <v>1.7914792899408443</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B11">
         <f>SUM(B2:B10)</f>
         <v>35</v>
@@ -4530,9 +4527,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB0876DF-9524-4501-8B6C-7EB698F79759}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -4558,7 +4555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4603,7 +4600,7 @@
         <v>0.93414094602397701</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4648,7 +4645,7 @@
         <v>0.87261930703857027</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4686,7 +4683,7 @@
         <v>47.95338294414497</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4724,7 +4721,7 @@
         <v>1.4901385239342084</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4766,7 +4763,7 @@
         <v>0.15423544067268763</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4804,7 +4801,7 @@
         <v>82.424495884186641</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4842,7 +4839,7 @@
         <v>6.924838116818691</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4879,7 +4876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4910,7 +4907,7 @@
         <v>1.960000000000016</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -4939,7 +4936,7 @@
         <v>493.99999999999989</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -4972,17 +4969,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D01BFC95-FB62-454A-8DFD-E6026B23C1F3}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="63" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -5023,7 +5020,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -5074,7 +5071,7 @@
         <v>497213.12955222564</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -5125,7 +5122,7 @@
         <v>273420.27683704928</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -5176,7 +5173,7 @@
         <v>125223.51660345681</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -5227,7 +5224,7 @@
         <v>22216.005175360388</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -5278,7 +5275,7 @@
         <v>3074.4754776926429</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -5329,7 +5326,7 @@
         <v>51041.240178272099</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -5380,7 +5377,7 @@
         <v>132540.58509537828</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -5431,7 +5428,7 @@
         <v>316847.90630395117</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -5482,7 +5479,7 @@
         <v>401348.01879626035</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -5497,7 +5494,7 @@
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A12" s="8" t="s">
         <v>34</v>
       </c>
@@ -5550,7 +5547,7 @@
         <v>1822925.1540196468</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A13" s="8" t="s">
         <v>35</v>
       </c>
@@ -5570,23 +5567,23 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A15" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="9">
         <f>$C$12</f>
         <v>14724</v>
@@ -5628,7 +5625,7 @@
         <v>12.425300000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="9">
         <f>$G$12</f>
         <v>17871.77</v>
@@ -5670,7 +5667,7 @@
         <v>16.938029</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="9">
         <f>$H$12</f>
         <v>23824.349900000005</v>
@@ -5712,7 +5709,7 @@
         <v>24.819190610000007</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -5728,7 +5725,7 @@
         <v>-714.69362941446605</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -5744,7 +5741,7 @@
         <v>3125.7484879169415</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -5760,7 +5757,7 @@
         <v>-815.47324405191284</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -5769,13 +5766,13 @@
         <v>-1312.1030221199583</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="30"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="35"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -5784,13 +5781,13 @@
         <v>0.98829366545865538</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="31"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="36"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -5799,7 +5796,7 @@
         <v>8.2291781925914204E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -5822,12 +5819,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C892A349-E08C-4EF9-852D-1395A2DE412E}">
   <dimension ref="A1:Z19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5868,7 +5865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5916,7 +5913,7 @@
         <v>43.133388144978369</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5954,7 +5951,7 @@
         <v>33.585469199230083</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5992,7 +5989,7 @@
         <v>29.133759613733172</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6030,7 +6027,7 @@
         <v>35.049563985434901</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6068,7 +6065,7 @@
         <v>34.327235344009537</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6106,7 +6103,7 @@
         <v>30.204850598711925</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6144,7 +6141,7 @@
         <v>21.311169892708786</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6182,7 +6179,7 @@
         <v>23.311883461595887</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -6223,7 +6220,7 @@
         <v>241.1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.45">
       <c r="L12">
         <v>8</v>
       </c>
@@ -6261,7 +6258,7 @@
         <v>241.1</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.45">
       <c r="L13">
         <v>127.5</v>
       </c>
@@ -6299,7 +6296,7 @@
         <v>3986.43</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.45">
       <c r="L14">
         <v>112.6</v>
       </c>
@@ -6337,7 +6334,7 @@
         <v>3315.15</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.45">
       <c r="L16" t="s">
         <v>37</v>
       </c>
@@ -6346,7 +6343,7 @@
         <v>17035.187800000309</v>
       </c>
     </row>
-    <row r="17" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="12:16" x14ac:dyDescent="0.45">
       <c r="L17" t="s">
         <v>59</v>
       </c>
@@ -6362,7 +6359,7 @@
         <v>43.133388144977403</v>
       </c>
     </row>
-    <row r="18" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="12:16" x14ac:dyDescent="0.45">
       <c r="L18" t="s">
         <v>60</v>
       </c>
@@ -6378,7 +6375,7 @@
         <v>0.52906632470468085</v>
       </c>
     </row>
-    <row r="19" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="12:16" x14ac:dyDescent="0.45">
       <c r="L19" t="s">
         <v>61</v>
       </c>
@@ -6407,9 +6404,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C4660E-B09C-4B66-8E8A-7F5AFFC18A2A}">
   <dimension ref="A1:AM35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:39" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="81" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>62</v>
       </c>
@@ -6474,7 +6471,7 @@
       <c r="AL1" s="15"/>
       <c r="AM1" s="15"/>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -6547,7 +6544,7 @@
       <c r="AL2" s="15"/>
       <c r="AM2" s="15"/>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -6620,7 +6617,7 @@
       <c r="AL3" s="15"/>
       <c r="AM3" s="15"/>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A4" s="11">
         <v>3</v>
       </c>
@@ -6693,7 +6690,7 @@
       <c r="AL4" s="15"/>
       <c r="AM4" s="15"/>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -6766,7 +6763,7 @@
       <c r="AL5" s="15"/>
       <c r="AM5" s="15"/>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -6839,7 +6836,7 @@
       <c r="AL6" s="15"/>
       <c r="AM6" s="15"/>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -6912,7 +6909,7 @@
       <c r="AL7" s="15"/>
       <c r="AM7" s="15"/>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -6985,7 +6982,7 @@
       <c r="AL8" s="15"/>
       <c r="AM8" s="15"/>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -7058,7 +7055,7 @@
       <c r="AL9" s="15"/>
       <c r="AM9" s="15"/>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -7099,7 +7096,7 @@
       <c r="AL10" s="15"/>
       <c r="AM10" s="15"/>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A11" s="11"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -7140,7 +7137,7 @@
       <c r="AL11" s="15"/>
       <c r="AM11" s="15"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -7216,7 +7213,7 @@
       <c r="AL12" s="15"/>
       <c r="AM12" s="15"/>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A13" s="15" t="s">
         <v>74</v>
       </c>
@@ -7292,7 +7289,7 @@
       <c r="AL13" s="15"/>
       <c r="AM13" s="15"/>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -7333,7 +7330,7 @@
       <c r="AL14" s="15"/>
       <c r="AM14" s="15"/>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A15" s="15">
         <f>$D$12</f>
         <v>241.1</v>
@@ -7413,7 +7410,7 @@
       <c r="AL15" s="15"/>
       <c r="AM15" s="15"/>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A16" s="15">
         <f>$E$12</f>
         <v>3315.15</v>
@@ -7493,7 +7490,7 @@
       <c r="AL16" s="15"/>
       <c r="AM16" s="15"/>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A17" s="15">
         <f>$F$12</f>
         <v>3986.43</v>
@@ -7573,7 +7570,7 @@
       <c r="AL17" s="15"/>
       <c r="AM17" s="15"/>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -7614,7 +7611,7 @@
       <c r="AL18" s="15"/>
       <c r="AM18" s="15"/>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A19" s="15" t="s">
         <v>37</v>
       </c>
@@ -7665,7 +7662,7 @@
       <c r="AL19" s="15"/>
       <c r="AM19" s="15"/>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A20" s="15" t="s">
         <v>41</v>
       </c>
@@ -7716,7 +7713,7 @@
       <c r="AL20" s="15"/>
       <c r="AM20" s="15"/>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A21" s="15" t="s">
         <v>43</v>
       </c>
@@ -7767,7 +7764,7 @@
       <c r="AL21" s="15"/>
       <c r="AM21" s="15"/>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A22" s="15" t="s">
         <v>75</v>
       </c>
@@ -7813,7 +7810,7 @@
       <c r="AL22" s="15"/>
       <c r="AM22" s="15"/>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -7854,7 +7851,7 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="15"/>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A24" s="15" t="s">
         <v>76</v>
       </c>
@@ -7910,7 +7907,7 @@
       <c r="AL24" s="15"/>
       <c r="AM24" s="15"/>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A25" s="15" t="s">
         <v>78</v>
       </c>
@@ -7966,7 +7963,7 @@
       <c r="AL25" s="15"/>
       <c r="AM25" s="15"/>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A26" s="15" t="s">
         <v>81</v>
       </c>
@@ -8022,7 +8019,7 @@
       <c r="AL26" s="15"/>
       <c r="AM26" s="15"/>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A27" s="15" t="s">
         <v>84</v>
       </c>
@@ -8078,7 +8075,7 @@
       <c r="AL27" s="15"/>
       <c r="AM27" s="15"/>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A28" s="15" t="s">
         <v>87</v>
       </c>
@@ -8134,7 +8131,7 @@
       <c r="AL28" s="15"/>
       <c r="AM28" s="15"/>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A29" s="15" t="s">
         <v>90</v>
       </c>
@@ -8190,7 +8187,7 @@
       <c r="AL29" s="15"/>
       <c r="AM29" s="15"/>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A30" s="15" t="s">
         <v>93</v>
       </c>
@@ -8236,7 +8233,7 @@
       <c r="AL30" s="15"/>
       <c r="AM30" s="15"/>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A31" s="15" t="s">
         <v>23</v>
       </c>
@@ -8282,7 +8279,7 @@
       <c r="AL31" s="15"/>
       <c r="AM31" s="15"/>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A32" s="15"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -8323,7 +8320,7 @@
       <c r="AL32" s="15"/>
       <c r="AM32" s="15"/>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A33" s="15"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -8364,7 +8361,7 @@
       <c r="AL33" s="15"/>
       <c r="AM33" s="15"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -8405,7 +8402,7 @@
       <c r="AL34" s="15"/>
       <c r="AM34" s="15"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -8454,68 +8451,68 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A54F079-9C03-45D4-8F74-6F1D0E70EA0F}">
   <dimension ref="A1:T98"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.86328125" customWidth="1"/>
+    <col min="2" max="2" width="11.1328125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" customWidth="1"/>
+    <col min="5" max="5" width="13.1328125" customWidth="1"/>
+    <col min="6" max="6" width="15.1328125" customWidth="1"/>
+    <col min="7" max="7" width="8.73046875" customWidth="1"/>
+    <col min="8" max="8" width="15.1328125" customWidth="1"/>
+    <col min="9" max="9" width="8.73046875" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" customWidth="1"/>
-    <col min="15" max="20" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="8.73046875" customWidth="1"/>
+    <col min="12" max="12" width="13.3984375" customWidth="1"/>
+    <col min="13" max="13" width="17.73046875" customWidth="1"/>
+    <col min="14" max="14" width="12.3984375" customWidth="1"/>
+    <col min="15" max="20" width="8.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="36" t="s">
+      <c r="F1" s="31"/>
+      <c r="G1" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="36" t="s">
+      <c r="H1" s="31"/>
+      <c r="I1" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="32" t="s">
+      <c r="J1" s="31"/>
+      <c r="K1" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="33"/>
+      <c r="L1" s="31"/>
       <c r="M1" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="N1" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="33"/>
+      <c r="O1" s="31"/>
       <c r="P1" s="24"/>
       <c r="Q1" s="24"/>
       <c r="R1" s="24"/>
       <c r="S1" s="24"/>
       <c r="T1" s="24"/>
     </row>
-    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
+    <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
       <c r="C2" s="21" t="s">
         <v>104</v>
       </c>
@@ -8561,7 +8558,7 @@
       <c r="S2" s="24"/>
       <c r="T2" s="24"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A3" s="25">
         <v>1</v>
       </c>
@@ -8615,7 +8612,7 @@
       <c r="S3" s="24"/>
       <c r="T3" s="24"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A4" s="25">
         <v>2</v>
       </c>
@@ -8680,7 +8677,7 @@
       <c r="S4" s="24"/>
       <c r="T4" s="24"/>
     </row>
-    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A5" s="25">
         <v>3</v>
       </c>
@@ -8745,7 +8742,7 @@
       <c r="S5" s="24"/>
       <c r="T5" s="24"/>
     </row>
-    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A6" s="25">
         <v>4</v>
       </c>
@@ -8810,7 +8807,7 @@
       <c r="S6" s="24"/>
       <c r="T6" s="24"/>
     </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A7" s="25">
         <v>5</v>
       </c>
@@ -8875,7 +8872,7 @@
       <c r="S7" s="24"/>
       <c r="T7" s="24"/>
     </row>
-    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A8" s="25">
         <v>6</v>
       </c>
@@ -8940,7 +8937,7 @@
       <c r="S8" s="24"/>
       <c r="T8" s="24"/>
     </row>
-    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A9" s="25">
         <v>7</v>
       </c>
@@ -9005,7 +9002,7 @@
       <c r="S9" s="24"/>
       <c r="T9" s="24"/>
     </row>
-    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A10" s="27" t="s">
         <v>73</v>
       </c>
@@ -9071,7 +9068,7 @@
       <c r="S10" s="24"/>
       <c r="T10" s="24"/>
     </row>
-    <row r="11" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="22" t="s">
         <v>108</v>
       </c>
@@ -9137,7 +9134,7 @@
       <c r="S11" s="24"/>
       <c r="T11" s="24"/>
     </row>
-    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A12" s="24"/>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -9159,7 +9156,7 @@
       <c r="S12" s="24"/>
       <c r="T12" s="24"/>
     </row>
-    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A13" s="24" t="s">
         <v>109</v>
       </c>
@@ -9186,7 +9183,7 @@
       <c r="S13" s="24"/>
       <c r="T13" s="24"/>
     </row>
-    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A14" s="24" t="s">
         <v>110</v>
       </c>
@@ -9213,7 +9210,7 @@
       <c r="S14" s="24"/>
       <c r="T14" s="24"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A15" s="24"/>
       <c r="B15" s="24"/>
       <c r="C15" s="24"/>
@@ -9235,15 +9232,15 @@
       <c r="S15" s="24"/>
       <c r="T15" s="24"/>
     </row>
-    <row r="16" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="24"/>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
       <c r="I16" s="24"/>
@@ -9259,7 +9256,7 @@
       <c r="S16" s="24"/>
       <c r="T16" s="24"/>
     </row>
-    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A17" s="24"/>
       <c r="B17" s="24" t="s">
         <v>112</v>
@@ -9289,7 +9286,7 @@
       <c r="S17" s="24"/>
       <c r="T17" s="24"/>
     </row>
-    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A18" s="24">
         <v>1</v>
       </c>
@@ -9324,7 +9321,7 @@
       <c r="S18" s="24"/>
       <c r="T18" s="24"/>
     </row>
-    <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A19" s="24">
         <v>2</v>
       </c>
@@ -9359,7 +9356,7 @@
       <c r="S19" s="24"/>
       <c r="T19" s="24"/>
     </row>
-    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="24">
         <v>3</v>
       </c>
@@ -9394,7 +9391,7 @@
       <c r="S20" s="24"/>
       <c r="T20" s="24"/>
     </row>
-    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="24">
         <v>4</v>
       </c>
@@ -9429,7 +9426,7 @@
       <c r="S21" s="24"/>
       <c r="T21" s="24"/>
     </row>
-    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="24">
         <v>5</v>
       </c>
@@ -9464,7 +9461,7 @@
       <c r="S22" s="24"/>
       <c r="T22" s="24"/>
     </row>
-    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="24">
         <v>6</v>
       </c>
@@ -9499,7 +9496,7 @@
       <c r="S23" s="24"/>
       <c r="T23" s="24"/>
     </row>
-    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="24">
         <v>7</v>
       </c>
@@ -9534,7 +9531,7 @@
       <c r="S24" s="24"/>
       <c r="T24" s="24"/>
     </row>
-    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="24" t="s">
         <v>73</v>
       </c>
@@ -9570,7 +9567,7 @@
       <c r="S25" s="24"/>
       <c r="T25" s="24"/>
     </row>
-    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="24"/>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
@@ -9592,7 +9589,7 @@
       <c r="S26" s="24"/>
       <c r="T26" s="24"/>
     </row>
-    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="24" t="s">
         <v>15</v>
       </c>
@@ -9619,7 +9616,7 @@
       <c r="S27" s="24"/>
       <c r="T27" s="24"/>
     </row>
-    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="24" t="s">
         <v>16</v>
       </c>
@@ -9646,7 +9643,7 @@
       <c r="S28" s="24"/>
       <c r="T28" s="24"/>
     </row>
-    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="24"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -9668,7 +9665,7 @@
       <c r="S29" s="24"/>
       <c r="T29" s="24"/>
     </row>
-    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="24"/>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
@@ -9690,7 +9687,7 @@
       <c r="S30" s="24"/>
       <c r="T30" s="24"/>
     </row>
-    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="24"/>
       <c r="B31" s="24"/>
       <c r="C31" s="24"/>
@@ -9712,7 +9709,7 @@
       <c r="S31" s="24"/>
       <c r="T31" s="24"/>
     </row>
-    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="24"/>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -9734,7 +9731,7 @@
       <c r="S32" s="24"/>
       <c r="T32" s="24"/>
     </row>
-    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="24"/>
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
@@ -9756,7 +9753,7 @@
       <c r="S33" s="24"/>
       <c r="T33" s="24"/>
     </row>
-    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="24"/>
       <c r="B34" s="24"/>
       <c r="C34" s="24"/>
@@ -9778,7 +9775,7 @@
       <c r="S34" s="24"/>
       <c r="T34" s="24"/>
     </row>
-    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="24"/>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
@@ -9800,7 +9797,7 @@
       <c r="S35" s="24"/>
       <c r="T35" s="24"/>
     </row>
-    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="24"/>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
@@ -9822,7 +9819,7 @@
       <c r="S36" s="24"/>
       <c r="T36" s="24"/>
     </row>
-    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="29" t="s">
         <v>114</v>
       </c>
@@ -9846,7 +9843,7 @@
       <c r="S37" s="24"/>
       <c r="T37" s="24"/>
     </row>
-    <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="29">
         <v>7</v>
       </c>
@@ -9870,66 +9867,66 @@
       <c r="S38" s="24"/>
       <c r="T38" s="24"/>
     </row>
-    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="40" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="42" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="43" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="44" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="45" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="K1:L1"/>
